--- a/data/export/2026-10-02-浦东78路.xlsx
+++ b/data/export/2026-10-02-浦东78路.xlsx
@@ -427,12 +427,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC4"/>
+  <dimension ref="A1:AC12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -441,7 +441,7 @@
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
     <col width="26" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="25" customWidth="1" min="12" max="12"/>
     <col width="22" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
@@ -632,32 +632,36 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:37</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -665,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -689,33 +693,37 @@
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB2" s="2" t="inlineStr"/>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>—/3</t>
+          <t>1/9</t>
         </is>
       </c>
     </row>
@@ -723,22 +731,22 @@
       <c r="A3" s="2" t="inlineStr"/>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A35186D</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>06:45</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -771,12 +779,12 @@
       <c r="M3" s="2" t="inlineStr"/>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -790,7 +798,7 @@
       <c r="T3" s="2" t="inlineStr"/>
       <c r="U3" s="2" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="V3" s="2" t="inlineStr">
@@ -815,7 +823,7 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -826,7 +834,7 @@
       <c r="AB3" s="2" t="inlineStr"/>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>—/3</t>
+          <t>—/9</t>
         </is>
       </c>
     </row>
@@ -834,7 +842,7 @@
       <c r="A4" s="2" t="inlineStr"/>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A59117D</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -844,7 +852,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>06:45</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -887,7 +895,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -901,7 +909,7 @@
       <c r="T4" s="2" t="inlineStr"/>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>06:45</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
@@ -937,7 +945,907 @@
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/3</t>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr"/>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>90分钟</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr"/>
+      <c r="K5" s="2" t="inlineStr"/>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr"/>
+      <c r="R5" s="2" t="inlineStr"/>
+      <c r="S5" s="2" t="inlineStr"/>
+      <c r="T5" s="2" t="inlineStr"/>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W5" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X5" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Y5" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z5" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="AC5" s="2" t="inlineStr">
+        <is>
+          <t>2/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr"/>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr"/>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr"/>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr"/>
+      <c r="R6" s="2" t="inlineStr"/>
+      <c r="S6" s="2" t="inlineStr"/>
+      <c r="T6" s="2" t="inlineStr"/>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W6" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X6" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y6" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z6" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB6" s="2" t="inlineStr"/>
+      <c r="AC6" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr"/>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr"/>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr"/>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr"/>
+      <c r="R7" s="2" t="inlineStr"/>
+      <c r="S7" s="2" t="inlineStr"/>
+      <c r="T7" s="2" t="inlineStr"/>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W7" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X7" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y7" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB7" s="2" t="inlineStr"/>
+      <c r="AC7" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr"/>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr"/>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr"/>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr"/>
+      <c r="R8" s="2" t="inlineStr"/>
+      <c r="S8" s="2" t="inlineStr"/>
+      <c r="T8" s="2" t="inlineStr"/>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W8" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X8" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y8" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z8" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AC8" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr"/>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="inlineStr"/>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr"/>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr"/>
+      <c r="R9" s="2" t="inlineStr"/>
+      <c r="S9" s="2" t="inlineStr"/>
+      <c r="T9" s="2" t="inlineStr"/>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W9" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X9" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y9" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z9" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB9" s="2" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
+      <c r="AC9" s="2" t="inlineStr">
+        <is>
+          <t>1/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr"/>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr"/>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr"/>
+      <c r="R10" s="2" t="inlineStr"/>
+      <c r="S10" s="2" t="inlineStr"/>
+      <c r="T10" s="2" t="inlineStr"/>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y10" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB10" s="2" t="inlineStr"/>
+      <c r="AC10" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr"/>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr"/>
+      <c r="R11" s="2" t="inlineStr"/>
+      <c r="S11" s="2" t="inlineStr"/>
+      <c r="T11" s="2" t="inlineStr"/>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y11" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AC11" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr"/>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr"/>
+      <c r="R12" s="2" t="inlineStr"/>
+      <c r="S12" s="2" t="inlineStr"/>
+      <c r="T12" s="2" t="inlineStr"/>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y12" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z12" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr"/>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-02-浦东78路.xlsx
+++ b/data/export/2026-10-02-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC12"/>
+  <dimension ref="A1:AC17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -642,24 +642,24 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>07:37</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>77分钟</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -718,12 +718,12 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>1/9</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -751,32 +751,36 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -784,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -808,17 +812,17 @@
       </c>
       <c r="W3" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z3" s="2" t="inlineStr">
@@ -828,13 +832,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
+          <t>71.0</t>
+        </is>
+      </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -862,32 +870,36 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:03</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -895,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -919,33 +931,37 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" s="2" t="inlineStr"/>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
+          <t>78.0</t>
+        </is>
+      </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -983,12 +999,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:26</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>90分钟</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
@@ -1010,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1049,22 +1065,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>2/9</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -1125,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1164,7 +1180,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1175,7 +1191,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/11</t>
         </is>
       </c>
     </row>
@@ -1203,32 +1219,36 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -1236,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1260,17 +1280,17 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
@@ -1280,13 +1300,17 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB7" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1371,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1397,7 +1421,7 @@
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/11</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1482,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1507,12 +1531,12 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>1/9</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -1573,7 +1597,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1623,7 +1647,7 @@
       <c r="AB10" s="2" t="inlineStr"/>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/11</t>
         </is>
       </c>
     </row>
@@ -1684,7 +1708,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1734,7 +1758,7 @@
       <c r="AB11" s="2" t="inlineStr"/>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/11</t>
         </is>
       </c>
     </row>
@@ -1795,7 +1819,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1839,13 +1863,580 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
+          <t>71.0</t>
+        </is>
+      </c>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>1/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr"/>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr"/>
+      <c r="R13" s="2" t="inlineStr"/>
+      <c r="S13" s="2" t="inlineStr"/>
+      <c r="T13" s="2" t="inlineStr"/>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y13" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
+          <t>78.0</t>
+        </is>
+      </c>
+      <c r="AC13" s="2" t="inlineStr">
+        <is>
+          <t>3/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr"/>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>07:50</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr"/>
+      <c r="R14" s="2" t="inlineStr"/>
+      <c r="S14" s="2" t="inlineStr"/>
+      <c r="T14" s="2" t="inlineStr"/>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y14" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB12" s="2" t="inlineStr"/>
-      <c r="AC12" s="2" t="inlineStr">
-        <is>
-          <t>—/9</t>
+      <c r="AB14" s="2" t="inlineStr"/>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>—/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr"/>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr"/>
+      <c r="R15" s="2" t="inlineStr"/>
+      <c r="S15" s="2" t="inlineStr"/>
+      <c r="T15" s="2" t="inlineStr"/>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W15" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y15" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z15" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
+          <t>5/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr"/>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr"/>
+      <c r="R16" s="2" t="inlineStr"/>
+      <c r="S16" s="2" t="inlineStr"/>
+      <c r="T16" s="2" t="inlineStr"/>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y16" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr"/>
+      <c r="AC16" s="2" t="inlineStr">
+        <is>
+          <t>—/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr"/>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>08:47</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr"/>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr"/>
+      <c r="R17" s="2" t="inlineStr"/>
+      <c r="S17" s="2" t="inlineStr"/>
+      <c r="T17" s="2" t="inlineStr"/>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>08:47</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y17" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z17" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr"/>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>—/11</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-02-浦东78路.xlsx
+++ b/data/export/2026-10-02-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC17"/>
+  <dimension ref="A1:AC27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,22 +708,22 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,22 +946,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1191,7 +1191,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>—/15</t>
         </is>
       </c>
     </row>
@@ -1229,24 +1229,24 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>85分钟</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1305,12 +1305,12 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -1338,32 +1338,36 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -1371,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1395,33 +1399,37 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -1449,32 +1457,36 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -1482,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1506,37 +1518,37 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA9" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -1564,32 +1576,36 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -1597,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1621,33 +1637,37 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB10" s="2" t="inlineStr"/>
+      <c r="AB10" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -1675,32 +1695,36 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
           <t>07:10</t>
@@ -1708,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1732,33 +1756,37 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AB11" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -1819,7 +1847,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1858,7 +1886,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -1873,7 +1901,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -1901,32 +1929,36 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr"/>
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -1934,7 +1966,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1958,37 +1990,37 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -2049,7 +2081,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2099,7 +2131,7 @@
       <c r="AB14" s="2" t="inlineStr"/>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>—/15</t>
         </is>
       </c>
     </row>
@@ -2160,7 +2192,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2214,7 +2246,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -2275,7 +2307,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2325,7 +2357,7 @@
       <c r="AB16" s="2" t="inlineStr"/>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>—/15</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2468,1141 @@
       <c r="AB17" s="2" t="inlineStr"/>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr"/>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>沪A53629D</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr"/>
+      <c r="R18" s="2" t="inlineStr"/>
+      <c r="S18" s="2" t="inlineStr"/>
+      <c r="T18" s="2" t="inlineStr"/>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W18" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y18" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z18" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr"/>
+      <c r="AC18" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr"/>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr"/>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr"/>
+      <c r="R19" s="2" t="inlineStr"/>
+      <c r="S19" s="2" t="inlineStr"/>
+      <c r="T19" s="2" t="inlineStr"/>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y19" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr"/>
+      <c r="AC19" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr"/>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr"/>
+      <c r="R20" s="2" t="inlineStr"/>
+      <c r="S20" s="2" t="inlineStr"/>
+      <c r="T20" s="2" t="inlineStr"/>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y20" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB20" s="2" t="inlineStr"/>
+      <c r="AC20" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr"/>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr"/>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr"/>
+      <c r="R21" s="2" t="inlineStr"/>
+      <c r="S21" s="2" t="inlineStr"/>
+      <c r="T21" s="2" t="inlineStr"/>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W21" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y21" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z21" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr"/>
+      <c r="AC21" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr"/>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr"/>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr"/>
+      <c r="R22" s="2" t="inlineStr"/>
+      <c r="S22" s="2" t="inlineStr"/>
+      <c r="T22" s="2" t="inlineStr"/>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y22" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="AC22" s="2" t="inlineStr">
+        <is>
+          <t>3/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr"/>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr"/>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr"/>
+      <c r="R23" s="2" t="inlineStr"/>
+      <c r="S23" s="2" t="inlineStr"/>
+      <c r="T23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
+      <c r="AC23" s="2" t="inlineStr">
+        <is>
+          <t>8/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr"/>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr"/>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr"/>
+      <c r="R24" s="2" t="inlineStr"/>
+      <c r="S24" s="2" t="inlineStr"/>
+      <c r="T24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
+          <t>76.5</t>
+        </is>
+      </c>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
+          <t>2/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr"/>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr"/>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr"/>
+      <c r="R25" s="2" t="inlineStr"/>
+      <c r="S25" s="2" t="inlineStr"/>
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>71.0</t>
+        </is>
+      </c>
+      <c r="AC25" s="2" t="inlineStr">
+        <is>
+          <t>1/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr"/>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr"/>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr"/>
+      <c r="R26" s="2" t="inlineStr"/>
+      <c r="S26" s="2" t="inlineStr"/>
+      <c r="T26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>5/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr"/>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr"/>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr"/>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr"/>
+      <c r="R27" s="2" t="inlineStr"/>
+      <c r="S27" s="2" t="inlineStr"/>
+      <c r="T27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>80.5</t>
+        </is>
+      </c>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>4/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-02-浦东78路.xlsx
+++ b/data/export/2026-10-02-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC27"/>
+  <dimension ref="A1:AC28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -832,12 +832,12 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1613,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1814,32 +1814,36 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -1847,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1871,17 +1875,17 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
@@ -1891,12 +1895,12 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
@@ -1966,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2081,7 +2085,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2192,7 +2196,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2231,7 +2235,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2307,7 +2311,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2529,7 +2533,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2640,7 +2644,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2751,7 +2755,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2862,7 +2866,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2973,7 +2977,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3088,7 +3092,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3203,7 +3207,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3318,7 +3322,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3362,12 +3366,12 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
@@ -3433,7 +3437,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3495,22 +3499,22 @@
       <c r="A27" s="2" t="inlineStr"/>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A55207D</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -3543,12 +3547,12 @@
       <c r="M27" s="2" t="inlineStr"/>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3562,45 +3566,160 @@
       <c r="T27" s="2" t="inlineStr"/>
       <c r="U27" s="2" t="inlineStr">
         <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>7/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr"/>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
           <t>10:00</t>
         </is>
       </c>
-      <c r="V27" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr"/>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr"/>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr"/>
+      <c r="R28" s="2" t="inlineStr"/>
+      <c r="S28" s="2" t="inlineStr"/>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W27" s="2" t="inlineStr">
+      <c r="W28" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X27" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Y27" s="2" t="inlineStr">
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z27" s="2" t="inlineStr">
+      <c r="Z28" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA27" s="2" t="inlineStr">
+      <c r="AA28" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB27" s="2" t="inlineStr">
+      <c r="AB28" s="2" t="inlineStr">
         <is>
           <t>80.5</t>
         </is>
       </c>
-      <c r="AC27" s="2" t="inlineStr">
+      <c r="AC28" s="2" t="inlineStr">
         <is>
           <t>4/15</t>
         </is>

--- a/data/export/2026-10-02-浦东78路.xlsx
+++ b/data/export/2026-10-02-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC28"/>
+  <dimension ref="A1:AC35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1185,13 +1185,17 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB6" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB6" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -1310,7 +1314,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1429,7 +1433,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1498,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1533,7 +1537,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
@@ -1548,7 +1552,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -1613,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1667,7 +1671,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1771,7 +1775,7 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -1786,7 +1790,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1905,7 +1909,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -1970,7 +1974,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2024,7 +2028,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -2052,32 +2056,36 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
           <t>07:50</t>
@@ -2085,7 +2093,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2109,33 +2117,37 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB14" s="2" t="inlineStr"/>
+      <c r="AB14" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -2196,7 +2208,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2250,7 +2262,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -2278,32 +2290,36 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr"/>
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -2311,7 +2327,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2335,17 +2351,17 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
@@ -2355,13 +2371,17 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB16" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -2500,32 +2520,36 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
           <t>08:20</t>
@@ -2533,7 +2557,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2557,33 +2581,37 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA18" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB18" s="2" t="inlineStr"/>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -2611,32 +2639,36 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr"/>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
           <t>08:20</t>
@@ -2644,7 +2676,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2668,33 +2700,37 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB19" s="2" t="inlineStr"/>
+      <c r="AB19" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -2722,32 +2758,36 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
           <t>08:40</t>
@@ -2755,7 +2795,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2779,33 +2819,37 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB20" s="2" t="inlineStr"/>
+      <c r="AB20" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -2866,7 +2910,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2905,7 +2949,7 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
@@ -2977,7 +3021,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3031,7 +3075,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -3092,7 +3136,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3146,7 +3190,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -3207,7 +3251,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3246,7 +3290,7 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
@@ -3261,7 +3305,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -3322,7 +3366,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3376,7 +3420,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -3437,7 +3481,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3476,7 +3520,7 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
@@ -3491,7 +3535,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -3552,7 +3596,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3606,7 +3650,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -3667,7 +3711,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3721,7 +3765,808 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
+          <t>7/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr"/>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>沪A53629D</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr"/>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr"/>
+      <c r="R29" s="2" t="inlineStr"/>
+      <c r="S29" s="2" t="inlineStr"/>
+      <c r="T29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="AC29" s="2" t="inlineStr">
+        <is>
+          <t>3/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr"/>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr"/>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>07:50</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr"/>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr">
+        <is>
+          <t>5/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr"/>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr"/>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr"/>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr"/>
+      <c r="R31" s="2" t="inlineStr"/>
+      <c r="S31" s="2" t="inlineStr"/>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr"/>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr"/>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr"/>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr"/>
+      <c r="R32" s="2" t="inlineStr"/>
+      <c r="S32" s="2" t="inlineStr"/>
+      <c r="T32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z32" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
+      <c r="AC32" s="2" t="inlineStr">
+        <is>
+          <t>1/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr"/>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr"/>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr"/>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr"/>
+      <c r="R33" s="2" t="inlineStr"/>
+      <c r="S33" s="2" t="inlineStr"/>
+      <c r="T33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z33" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
+          <t>76.5</t>
+        </is>
+      </c>
+      <c r="AC33" s="2" t="inlineStr">
+        <is>
           <t>4/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr"/>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr"/>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr"/>
+      <c r="R34" s="2" t="inlineStr"/>
+      <c r="S34" s="2" t="inlineStr"/>
+      <c r="T34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="AC34" s="2" t="inlineStr">
+        <is>
+          <t>10/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr"/>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr"/>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr"/>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr"/>
+      <c r="R35" s="2" t="inlineStr"/>
+      <c r="S35" s="2" t="inlineStr"/>
+      <c r="T35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AC35" s="2" t="inlineStr">
+        <is>
+          <t>8/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-02-浦东78路.xlsx
+++ b/data/export/2026-10-02-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC35"/>
+  <dimension ref="A1:AC41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,22 +946,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1070,7 +1070,7 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -1314,7 +1314,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1418,14 +1418,14 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
           <t>80.0</t>
@@ -1433,7 +1433,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1671,7 +1671,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1780,7 +1780,7 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
@@ -1790,7 +1790,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -1855,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -1909,7 +1909,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2013,22 +2013,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -2093,7 +2093,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2147,7 +2147,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -2381,7 +2381,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -2557,7 +2557,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2596,22 +2596,22 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA18" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2730,7 +2730,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -2768,24 +2768,24 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>84分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2795,7 +2795,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2844,12 +2844,12 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -2877,32 +2877,36 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr"/>
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
           <t>08:20</t>
@@ -2910,7 +2914,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2934,17 +2938,17 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z21" s="2" t="inlineStr">
@@ -2954,13 +2958,17 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB21" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -2988,32 +2996,36 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr"/>
       <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -3021,7 +3033,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3045,29 +3057,29 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y22" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
           <t>80.0</t>
@@ -3075,7 +3087,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3148,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3190,7 +3202,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -3251,7 +3263,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3366,7 +3378,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3405,7 +3417,7 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
@@ -3420,7 +3432,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -3448,32 +3460,36 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr"/>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
           <t>07:10</t>
@@ -3481,7 +3497,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3505,17 +3521,17 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
@@ -3525,7 +3541,7 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
@@ -3535,7 +3551,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -3563,32 +3579,36 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr"/>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -3596,7 +3616,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3620,17 +3640,17 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
@@ -3640,7 +3660,7 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
@@ -3650,7 +3670,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -3678,32 +3698,36 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -3711,7 +3735,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3735,37 +3759,37 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA28" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -3793,32 +3817,36 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr"/>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
           <t>08:20</t>
@@ -3826,7 +3854,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3850,37 +3878,37 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA29" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -3941,7 +3969,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3980,7 +4008,7 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
@@ -3995,7 +4023,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -4056,7 +4084,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4100,13 +4128,17 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB31" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -4167,7 +4199,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4206,7 +4238,7 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
@@ -4221,7 +4253,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -4282,7 +4314,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4397,7 +4429,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4446,12 +4478,12 @@
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -4512,7 +4544,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4556,17 +4588,707 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AC35" s="2" t="inlineStr">
+        <is>
+          <t>9/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr"/>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr"/>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr"/>
+      <c r="R36" s="2" t="inlineStr"/>
+      <c r="S36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="AC36" s="2" t="inlineStr">
+        <is>
+          <t>6/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr"/>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr"/>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr"/>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr"/>
+      <c r="R37" s="2" t="inlineStr"/>
+      <c r="S37" s="2" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
+          <t>78.0</t>
+        </is>
+      </c>
+      <c r="AC37" s="2" t="inlineStr">
+        <is>
+          <t>5/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr"/>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr"/>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>07:50</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr"/>
+      <c r="R38" s="2" t="inlineStr"/>
+      <c r="S38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB35" s="2" t="inlineStr">
-        <is>
-          <t>82.0</t>
-        </is>
-      </c>
-      <c r="AC35" s="2" t="inlineStr">
-        <is>
-          <t>8/15</t>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="AC38" s="2" t="inlineStr">
+        <is>
+          <t>6/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr"/>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr"/>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr"/>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr"/>
+      <c r="R39" s="2" t="inlineStr"/>
+      <c r="S39" s="2" t="inlineStr"/>
+      <c r="T39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>74.5</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>3/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr"/>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr"/>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr"/>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr"/>
+      <c r="R40" s="2" t="inlineStr"/>
+      <c r="S40" s="2" t="inlineStr"/>
+      <c r="T40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
+      <c r="AC40" s="2" t="inlineStr">
+        <is>
+          <t>2/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr"/>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>沪A53629D</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr"/>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr"/>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr"/>
+      <c r="R41" s="2" t="inlineStr"/>
+      <c r="S41" s="2" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
+      <c r="AC41" s="2" t="inlineStr">
+        <is>
+          <t>1/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-02-浦东78路.xlsx
+++ b/data/export/2026-10-02-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC41"/>
+  <dimension ref="A1:AC47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -713,17 +713,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>5/16</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>2/16</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>4/16</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>13/16</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1180,7 +1180,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>9/16</t>
         </is>
       </c>
     </row>
@@ -1314,7 +1314,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>12/16</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1418,22 +1418,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>6/16</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1542,17 +1542,17 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>5/16</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>14/16</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1780,17 +1780,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>8/16</t>
         </is>
       </c>
     </row>
@@ -1855,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -1909,7 +1909,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>2/16</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>4/16</t>
         </is>
       </c>
     </row>
@@ -2093,7 +2093,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2137,17 +2137,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>9/16</t>
         </is>
       </c>
     </row>
@@ -2262,7 +2262,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>13/16</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2327,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2366,7 +2366,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2381,7 +2381,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>9/16</t>
         </is>
       </c>
     </row>
@@ -2492,7 +2492,7 @@
       <c r="AB17" s="2" t="inlineStr"/>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/16</t>
         </is>
       </c>
     </row>
@@ -2557,7 +2557,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>1/16</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2720,17 +2720,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>3/16</t>
         </is>
       </c>
     </row>
@@ -2795,7 +2795,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2834,22 +2834,22 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>11/16</t>
         </is>
       </c>
     </row>
@@ -2914,7 +2914,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2953,22 +2953,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>7/16</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3072,22 +3072,22 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA22" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>6/16</t>
         </is>
       </c>
     </row>
@@ -3202,7 +3202,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>14/16</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3307,17 +3307,17 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>5/16</t>
         </is>
       </c>
     </row>
@@ -3378,7 +3378,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3417,7 +3417,7 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
@@ -3432,7 +3432,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>2/16</t>
         </is>
       </c>
     </row>
@@ -3497,7 +3497,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3541,17 +3541,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>8/16</t>
         </is>
       </c>
     </row>
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>13/16</t>
         </is>
       </c>
     </row>
@@ -3735,7 +3735,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3789,7 +3789,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>4/16</t>
         </is>
       </c>
     </row>
@@ -3854,7 +3854,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>1/16</t>
         </is>
       </c>
     </row>
@@ -3936,32 +3936,36 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
           <t>07:50</t>
@@ -3969,7 +3973,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3993,17 +3997,17 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z30" s="2" t="inlineStr">
@@ -4013,17 +4017,17 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>9/16</t>
         </is>
       </c>
     </row>
@@ -4051,32 +4055,36 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr"/>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
           <t>08:20</t>
@@ -4084,7 +4092,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4108,37 +4116,37 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA31" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>7/16</t>
         </is>
       </c>
     </row>
@@ -4166,32 +4174,36 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
           <t>08:20</t>
@@ -4199,7 +4211,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4223,17 +4235,17 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
@@ -4243,17 +4255,17 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>3/16</t>
         </is>
       </c>
     </row>
@@ -4281,32 +4293,36 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M33" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -4314,7 +4330,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4338,17 +4354,17 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
@@ -4358,17 +4374,17 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>5/16</t>
         </is>
       </c>
     </row>
@@ -4396,32 +4412,36 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
           <t>08:40</t>
@@ -4429,7 +4449,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4453,37 +4473,37 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA34" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>11/16</t>
         </is>
       </c>
     </row>
@@ -4511,32 +4531,36 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M35" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
           <t>07:10</t>
@@ -4544,7 +4568,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4568,17 +4592,17 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z35" s="2" t="inlineStr">
@@ -4588,17 +4612,17 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>8/16</t>
         </is>
       </c>
     </row>
@@ -4626,32 +4650,36 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -4659,7 +4687,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4683,37 +4711,37 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA36" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>6/16</t>
         </is>
       </c>
     </row>
@@ -4774,7 +4802,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4828,7 +4856,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>4/16</t>
         </is>
       </c>
     </row>
@@ -4889,7 +4917,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4933,17 +4961,17 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>9/16</t>
         </is>
       </c>
     </row>
@@ -5004,7 +5032,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5043,7 +5071,7 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
@@ -5058,7 +5086,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>2/16</t>
         </is>
       </c>
     </row>
@@ -5119,7 +5147,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5163,17 +5191,17 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>3/16</t>
         </is>
       </c>
     </row>
@@ -5234,7 +5262,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5288,7 +5316,693 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>1/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr"/>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr"/>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr"/>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr"/>
+      <c r="R42" s="2" t="inlineStr"/>
+      <c r="S42" s="2" t="inlineStr"/>
+      <c r="T42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
+          <t>82.5</t>
+        </is>
+      </c>
+      <c r="AC42" s="2" t="inlineStr">
+        <is>
+          <t>11/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr"/>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr"/>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr"/>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr"/>
+      <c r="R43" s="2" t="inlineStr"/>
+      <c r="S43" s="2" t="inlineStr"/>
+      <c r="T43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z43" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB43" s="2" t="inlineStr">
+        <is>
+          <t>80.5</t>
+        </is>
+      </c>
+      <c r="AC43" s="2" t="inlineStr">
+        <is>
+          <t>7/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr"/>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr"/>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr"/>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr"/>
+      <c r="R44" s="2" t="inlineStr"/>
+      <c r="S44" s="2" t="inlineStr"/>
+      <c r="T44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z44" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr">
+        <is>
+          <t>78.7</t>
+        </is>
+      </c>
+      <c r="AC44" s="2" t="inlineStr">
+        <is>
+          <t>6/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr"/>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr"/>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr"/>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr"/>
+      <c r="R45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr"/>
+      <c r="T45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr"/>
+      <c r="AC45" s="2" t="inlineStr">
+        <is>
+          <t>—/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr"/>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr"/>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr"/>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr"/>
+      <c r="R46" s="2" t="inlineStr"/>
+      <c r="S46" s="2" t="inlineStr"/>
+      <c r="T46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr">
+        <is>
+          <t>74.5</t>
+        </is>
+      </c>
+      <c r="AC46" s="2" t="inlineStr">
+        <is>
+          <t>2/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr"/>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr"/>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr"/>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr"/>
+      <c r="R47" s="2" t="inlineStr"/>
+      <c r="S47" s="2" t="inlineStr"/>
+      <c r="T47" s="2" t="inlineStr"/>
+      <c r="U47" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z47" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AC47" s="2" t="inlineStr">
+        <is>
+          <t>9/16</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-02-浦东78路.xlsx
+++ b/data/export/2026-10-02-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC47"/>
+  <dimension ref="A1:AC52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -832,12 +832,12 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>4/16</t>
+          <t>3/16</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>9/16</t>
+          <t>11/16</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>6/16</t>
+          <t>3/16</t>
         </is>
       </c>
     </row>
@@ -1617,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1790,7 +1790,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>8/16</t>
+          <t>10/16</t>
         </is>
       </c>
     </row>
@@ -1855,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>4/16</t>
+          <t>3/16</t>
         </is>
       </c>
     </row>
@@ -2093,7 +2093,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
@@ -2208,7 +2208,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2247,7 +2247,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2327,7 +2327,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2381,7 +2381,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>9/16</t>
+          <t>11/16</t>
         </is>
       </c>
     </row>
@@ -2557,7 +2557,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2596,17 +2596,17 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA18" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
@@ -2676,7 +2676,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2720,17 +2720,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>3/16</t>
+          <t>5/16</t>
         </is>
       </c>
     </row>
@@ -2795,7 +2795,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2839,17 +2839,17 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>11/16</t>
+          <t>7/16</t>
         </is>
       </c>
     </row>
@@ -2914,7 +2914,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2953,7 +2953,7 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
@@ -2968,7 +2968,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>7/16</t>
+          <t>8/16</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3082,12 +3082,12 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>6/16</t>
+          <t>3/16</t>
         </is>
       </c>
     </row>
@@ -3148,7 +3148,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3187,7 +3187,7 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
@@ -3378,7 +3378,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3422,12 +3422,12 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
@@ -3551,7 +3551,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>8/16</t>
+          <t>10/16</t>
         </is>
       </c>
     </row>
@@ -3616,7 +3616,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3655,7 +3655,7 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
@@ -3735,7 +3735,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3789,7 +3789,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>4/16</t>
+          <t>3/16</t>
         </is>
       </c>
     </row>
@@ -3854,7 +3854,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3893,17 +3893,17 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA29" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
@@ -3973,7 +3973,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4017,12 +4017,12 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
@@ -4092,7 +4092,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4131,7 +4131,7 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>7/16</t>
+          <t>8/16</t>
         </is>
       </c>
     </row>
@@ -4211,7 +4211,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4255,17 +4255,17 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>3/16</t>
+          <t>5/16</t>
         </is>
       </c>
     </row>
@@ -4449,7 +4449,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4493,17 +4493,17 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>11/16</t>
+          <t>7/16</t>
         </is>
       </c>
     </row>
@@ -4622,7 +4622,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>8/16</t>
+          <t>10/16</t>
         </is>
       </c>
     </row>
@@ -4660,12 +4660,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>76分钟</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
@@ -4687,7 +4687,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4736,12 +4736,12 @@
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>6/16</t>
+          <t>3/16</t>
         </is>
       </c>
     </row>
@@ -4802,7 +4802,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4856,7 +4856,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>4/16</t>
+          <t>3/16</t>
         </is>
       </c>
     </row>
@@ -4884,32 +4884,36 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M38" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
           <t>07:50</t>
@@ -4917,7 +4921,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4941,17 +4945,17 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
@@ -4961,12 +4965,12 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
@@ -4999,32 +5003,36 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M39" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -5032,7 +5040,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5056,17 +5064,17 @@
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
@@ -5076,12 +5084,12 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
@@ -5114,32 +5122,36 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
           <t>08:20</t>
@@ -5147,7 +5159,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5171,17 +5183,17 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
@@ -5191,17 +5203,17 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>3/16</t>
+          <t>5/16</t>
         </is>
       </c>
     </row>
@@ -5229,32 +5241,36 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr"/>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
           <t>08:20</t>
@@ -5262,7 +5278,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5286,32 +5302,32 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA41" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
@@ -5344,32 +5360,36 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
           <t>08:40</t>
@@ -5377,7 +5397,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5401,17 +5421,17 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr">
@@ -5421,17 +5441,17 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>11/16</t>
+          <t>7/16</t>
         </is>
       </c>
     </row>
@@ -5492,7 +5512,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5531,7 +5551,7 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
@@ -5546,7 +5566,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>7/16</t>
+          <t>8/16</t>
         </is>
       </c>
     </row>
@@ -5607,7 +5627,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5656,12 +5676,12 @@
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>6/16</t>
+          <t>3/16</t>
         </is>
       </c>
     </row>
@@ -5722,7 +5742,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5761,7 +5781,7 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
@@ -5833,7 +5853,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5877,12 +5897,12 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
@@ -5948,7 +5968,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6002,7 +6022,578 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>9/16</t>
+          <t>11/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr"/>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>沪A53629D</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr"/>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr"/>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr"/>
+      <c r="R48" s="2" t="inlineStr"/>
+      <c r="S48" s="2" t="inlineStr"/>
+      <c r="T48" s="2" t="inlineStr"/>
+      <c r="U48" s="2" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z48" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
+      <c r="AC48" s="2" t="inlineStr">
+        <is>
+          <t>1/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr"/>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr"/>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr"/>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr"/>
+      <c r="R49" s="2" t="inlineStr"/>
+      <c r="S49" s="2" t="inlineStr"/>
+      <c r="T49" s="2" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W49" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z49" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB49" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
+      <c r="AC49" s="2" t="inlineStr">
+        <is>
+          <t>13/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr"/>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr"/>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr"/>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr"/>
+      <c r="R50" s="2" t="inlineStr"/>
+      <c r="S50" s="2" t="inlineStr"/>
+      <c r="T50" s="2" t="inlineStr"/>
+      <c r="U50" s="2" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W50" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z50" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB50" s="2" t="inlineStr">
+        <is>
+          <t>80.5</t>
+        </is>
+      </c>
+      <c r="AC50" s="2" t="inlineStr">
+        <is>
+          <t>8/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr"/>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr"/>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr"/>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr"/>
+      <c r="R51" s="2" t="inlineStr"/>
+      <c r="S51" s="2" t="inlineStr"/>
+      <c r="T51" s="2" t="inlineStr"/>
+      <c r="U51" s="2" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W51" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z51" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB51" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
+      <c r="AC51" s="2" t="inlineStr">
+        <is>
+          <t>14/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr"/>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr"/>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr"/>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr"/>
+      <c r="R52" s="2" t="inlineStr"/>
+      <c r="S52" s="2" t="inlineStr"/>
+      <c r="T52" s="2" t="inlineStr"/>
+      <c r="U52" s="2" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W52" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z52" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB52" s="2" t="inlineStr"/>
+      <c r="AC52" s="2" t="inlineStr">
+        <is>
+          <t>—/16</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-02-浦东78路.xlsx
+++ b/data/export/2026-10-02-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC52"/>
+  <dimension ref="A1:AC57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>5/16</t>
+          <t>4/16</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,22 +827,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>2/16</t>
+          <t>6/16</t>
         </is>
       </c>
     </row>
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>3/16</t>
+          <t>2/16</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>13/16</t>
+          <t>14/16</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1180,12 +1180,12 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1418,17 +1418,17 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>5/16</t>
+          <t>4/16</t>
         </is>
       </c>
     </row>
@@ -1617,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1671,7 +1671,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>14/16</t>
+          <t>15/16</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1894,22 +1894,22 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>2/16</t>
+          <t>6/16</t>
         </is>
       </c>
     </row>
@@ -2028,7 +2028,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>3/16</t>
+          <t>2/16</t>
         </is>
       </c>
     </row>
@@ -2147,7 +2147,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>9/16</t>
+          <t>8/16</t>
         </is>
       </c>
     </row>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2247,7 +2247,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>13/16</t>
+          <t>14/16</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2327,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2366,12 +2366,12 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
@@ -2557,7 +2557,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
@@ -2730,7 +2730,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>5/16</t>
+          <t>4/16</t>
         </is>
       </c>
     </row>
@@ -2795,7 +2795,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2958,12 +2958,12 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
@@ -3033,7 +3033,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3072,17 +3072,17 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA22" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
@@ -3148,7 +3148,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3202,7 +3202,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>14/16</t>
+          <t>15/16</t>
         </is>
       </c>
     </row>
@@ -3317,7 +3317,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>5/16</t>
+          <t>4/16</t>
         </is>
       </c>
     </row>
@@ -3378,7 +3378,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3417,22 +3417,22 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>2/16</t>
+          <t>6/16</t>
         </is>
       </c>
     </row>
@@ -3497,7 +3497,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3536,7 +3536,7 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
@@ -3616,7 +3616,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3655,7 +3655,7 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>13/16</t>
+          <t>14/16</t>
         </is>
       </c>
     </row>
@@ -3789,7 +3789,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>3/16</t>
+          <t>2/16</t>
         </is>
       </c>
     </row>
@@ -3854,7 +3854,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3898,12 +3898,12 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
@@ -4027,7 +4027,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>9/16</t>
+          <t>8/16</t>
         </is>
       </c>
     </row>
@@ -4092,7 +4092,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
@@ -4265,7 +4265,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>5/16</t>
+          <t>4/16</t>
         </is>
       </c>
     </row>
@@ -4384,7 +4384,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>5/16</t>
+          <t>4/16</t>
         </is>
       </c>
     </row>
@@ -4449,7 +4449,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4568,7 +4568,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4607,7 +4607,7 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
@@ -4687,7 +4687,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4726,17 +4726,17 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA36" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
@@ -4856,7 +4856,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>3/16</t>
+          <t>2/16</t>
         </is>
       </c>
     </row>
@@ -4975,7 +4975,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>9/16</t>
+          <t>8/16</t>
         </is>
       </c>
     </row>
@@ -5040,7 +5040,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5079,22 +5079,22 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>2/16</t>
+          <t>6/16</t>
         </is>
       </c>
     </row>
@@ -5213,7 +5213,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>5/16</t>
+          <t>4/16</t>
         </is>
       </c>
     </row>
@@ -5278,7 +5278,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5322,12 +5322,12 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
@@ -5382,12 +5382,12 @@
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5397,7 +5397,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5479,32 +5479,36 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr"/>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
           <t>08:20</t>
@@ -5512,7 +5516,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5536,17 +5540,17 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z43" s="2" t="inlineStr">
@@ -5556,12 +5560,12 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
@@ -5594,32 +5598,36 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -5627,7 +5635,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5651,32 +5659,32 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y44" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA44" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5709,32 +5717,36 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M45" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
           <t>12:00</t>
@@ -5742,7 +5754,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5766,17 +5778,17 @@
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z45" s="2" t="inlineStr">
@@ -5786,13 +5798,17 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB45" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>—/16</t>
+          <t>12/16</t>
         </is>
       </c>
     </row>
@@ -5820,32 +5836,36 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -5853,7 +5873,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5877,37 +5897,37 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>2/16</t>
+          <t>6/16</t>
         </is>
       </c>
     </row>
@@ -5935,32 +5955,36 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr"/>
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M47" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -5968,7 +5992,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -5992,27 +6016,27 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y47" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
@@ -6050,32 +6074,36 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M48" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
           <t>08:20</t>
@@ -6083,7 +6111,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6107,17 +6135,17 @@
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y48" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z48" s="2" t="inlineStr">
@@ -6127,12 +6155,12 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
@@ -6198,7 +6226,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6237,7 +6265,7 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA49" s="2" t="inlineStr">
@@ -6252,7 +6280,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>13/16</t>
+          <t>14/16</t>
         </is>
       </c>
     </row>
@@ -6313,7 +6341,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6357,12 +6385,12 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
@@ -6428,7 +6456,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6482,7 +6510,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>14/16</t>
+          <t>15/16</t>
         </is>
       </c>
     </row>
@@ -6543,7 +6571,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6587,13 +6615,592 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB52" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB52" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>—/16</t>
+          <t>12/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr"/>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr"/>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr"/>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr"/>
+      <c r="R53" s="2" t="inlineStr"/>
+      <c r="S53" s="2" t="inlineStr"/>
+      <c r="T53" s="2" t="inlineStr"/>
+      <c r="U53" s="2" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W53" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z53" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr">
+        <is>
+          <t>81.3</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr">
+        <is>
+          <t>10/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr"/>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr"/>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr"/>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr"/>
+      <c r="R54" s="2" t="inlineStr"/>
+      <c r="S54" s="2" t="inlineStr"/>
+      <c r="T54" s="2" t="inlineStr"/>
+      <c r="U54" s="2" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z54" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
+          <t>78.2</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr">
+        <is>
+          <t>3/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr"/>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr"/>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr"/>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr"/>
+      <c r="R55" s="2" t="inlineStr"/>
+      <c r="S55" s="2" t="inlineStr"/>
+      <c r="T55" s="2" t="inlineStr"/>
+      <c r="U55" s="2" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W55" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z55" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="inlineStr">
+        <is>
+          <t>11/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr"/>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr"/>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr"/>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr"/>
+      <c r="R56" s="2" t="inlineStr"/>
+      <c r="S56" s="2" t="inlineStr"/>
+      <c r="T56" s="2" t="inlineStr"/>
+      <c r="U56" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W56" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z56" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB56" s="2" t="inlineStr">
+        <is>
+          <t>78.5</t>
+        </is>
+      </c>
+      <c r="AC56" s="2" t="inlineStr">
+        <is>
+          <t>6/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr"/>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr"/>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr"/>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr"/>
+      <c r="R57" s="2" t="inlineStr"/>
+      <c r="S57" s="2" t="inlineStr"/>
+      <c r="T57" s="2" t="inlineStr"/>
+      <c r="U57" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W57" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y57" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z57" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB57" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
+      <c r="AC57" s="2" t="inlineStr">
+        <is>
+          <t>14/16</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-02-浦东78路.xlsx
+++ b/data/export/2026-10-02-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC57"/>
+  <dimension ref="A1:AC63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>4/16</t>
+          <t>5/16</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>6/16</t>
+          <t>7/16</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1070,17 +1070,17 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>85.7</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>14/16</t>
+          <t>15/16</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1190,12 +1190,12 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>11/16</t>
+          <t>2/16</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>3/16</t>
+          <t>4/16</t>
         </is>
       </c>
     </row>
@@ -1552,7 +1552,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>4/16</t>
+          <t>5/16</t>
         </is>
       </c>
     </row>
@@ -1617,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1656,22 +1656,22 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>15/16</t>
+          <t>12/16</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -1790,7 +1790,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>10/16</t>
+          <t>11/16</t>
         </is>
       </c>
     </row>
@@ -1855,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1909,7 +1909,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>6/16</t>
+          <t>7/16</t>
         </is>
       </c>
     </row>
@@ -2093,7 +2093,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2132,14 +2132,14 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
           <t>80.7</t>
@@ -2147,7 +2147,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>8/16</t>
+          <t>9/16</t>
         </is>
       </c>
     </row>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2252,17 +2252,17 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>85.7</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>14/16</t>
+          <t>15/16</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2327,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2376,12 +2376,12 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>11/16</t>
+          <t>2/16</t>
         </is>
       </c>
     </row>
@@ -2557,7 +2557,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2596,17 +2596,17 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA18" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
@@ -2676,7 +2676,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2715,14 +2715,14 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA19" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
           <t>78.3</t>
@@ -2730,7 +2730,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>4/16</t>
+          <t>5/16</t>
         </is>
       </c>
     </row>
@@ -2849,7 +2849,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>7/16</t>
+          <t>8/16</t>
         </is>
       </c>
     </row>
@@ -2914,7 +2914,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2953,22 +2953,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>8/16</t>
+          <t>10/16</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3087,7 +3087,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>3/16</t>
+          <t>4/16</t>
         </is>
       </c>
     </row>
@@ -3148,7 +3148,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3187,22 +3187,22 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>15/16</t>
+          <t>12/16</t>
         </is>
       </c>
     </row>
@@ -3317,7 +3317,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>4/16</t>
+          <t>5/16</t>
         </is>
       </c>
     </row>
@@ -3378,7 +3378,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3432,7 +3432,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>6/16</t>
+          <t>7/16</t>
         </is>
       </c>
     </row>
@@ -3497,7 +3497,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3536,7 +3536,7 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
@@ -3551,7 +3551,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>10/16</t>
+          <t>11/16</t>
         </is>
       </c>
     </row>
@@ -3616,7 +3616,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3660,17 +3660,17 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>85.7</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>14/16</t>
+          <t>15/16</t>
         </is>
       </c>
     </row>
@@ -3854,7 +3854,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3893,17 +3893,17 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA29" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
@@ -3973,7 +3973,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4012,14 +4012,14 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA30" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
           <t>80.7</t>
@@ -4027,7 +4027,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>8/16</t>
+          <t>9/16</t>
         </is>
       </c>
     </row>
@@ -4092,7 +4092,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4131,22 +4131,22 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA31" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>8/16</t>
+          <t>10/16</t>
         </is>
       </c>
     </row>
@@ -4211,7 +4211,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4250,14 +4250,14 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA32" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
           <t>78.3</t>
@@ -4265,7 +4265,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>4/16</t>
+          <t>5/16</t>
         </is>
       </c>
     </row>
@@ -4384,7 +4384,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>4/16</t>
+          <t>5/16</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>7/16</t>
+          <t>8/16</t>
         </is>
       </c>
     </row>
@@ -4568,7 +4568,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4607,7 +4607,7 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
@@ -4622,7 +4622,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>10/16</t>
+          <t>11/16</t>
         </is>
       </c>
     </row>
@@ -4687,7 +4687,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4741,7 +4741,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>3/16</t>
+          <t>4/16</t>
         </is>
       </c>
     </row>
@@ -4921,7 +4921,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4960,14 +4960,14 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA38" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
           <t>80.7</t>
@@ -4975,7 +4975,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>8/16</t>
+          <t>9/16</t>
         </is>
       </c>
     </row>
@@ -5040,7 +5040,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5094,7 +5094,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>6/16</t>
+          <t>7/16</t>
         </is>
       </c>
     </row>
@@ -5159,7 +5159,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5198,14 +5198,14 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA40" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
           <t>78.3</t>
@@ -5213,7 +5213,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>4/16</t>
+          <t>5/16</t>
         </is>
       </c>
     </row>
@@ -5278,7 +5278,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5317,17 +5317,17 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA41" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
@@ -5451,7 +5451,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>7/16</t>
+          <t>8/16</t>
         </is>
       </c>
     </row>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5555,22 +5555,22 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA43" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>8/16</t>
+          <t>10/16</t>
         </is>
       </c>
     </row>
@@ -5635,7 +5635,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5689,7 +5689,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>3/16</t>
+          <t>4/16</t>
         </is>
       </c>
     </row>
@@ -5754,7 +5754,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5798,7 +5798,7 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
@@ -5873,7 +5873,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5927,7 +5927,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>6/16</t>
+          <t>7/16</t>
         </is>
       </c>
     </row>
@@ -5965,24 +5965,24 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr"/>
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5992,7 +5992,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6041,12 +6041,12 @@
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>11/16</t>
+          <t>2/16</t>
         </is>
       </c>
     </row>
@@ -6084,12 +6084,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>79分钟</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr"/>
@@ -6111,7 +6111,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6150,17 +6150,17 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA48" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
@@ -6193,32 +6193,36 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M49" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -6226,7 +6230,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6250,17 +6254,17 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y49" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z49" s="2" t="inlineStr">
@@ -6270,17 +6274,17 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>85.7</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>14/16</t>
+          <t>15/16</t>
         </is>
       </c>
     </row>
@@ -6308,32 +6312,36 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M50" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
           <t>08:20</t>
@@ -6341,7 +6349,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6365,37 +6373,37 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y50" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA50" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>8/16</t>
+          <t>10/16</t>
         </is>
       </c>
     </row>
@@ -6423,32 +6431,36 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M51" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -6456,7 +6468,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6480,37 +6492,37 @@
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y51" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>15/16</t>
+          <t>12/16</t>
         </is>
       </c>
     </row>
@@ -6538,32 +6550,36 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M52" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
           <t>12:00</t>
@@ -6571,7 +6587,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6595,17 +6611,17 @@
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y52" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z52" s="2" t="inlineStr">
@@ -6615,7 +6631,7 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
@@ -6686,7 +6702,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6725,7 +6741,7 @@
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA53" s="2" t="inlineStr">
@@ -6740,7 +6756,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>10/16</t>
+          <t>11/16</t>
         </is>
       </c>
     </row>
@@ -6801,7 +6817,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6855,7 +6871,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>3/16</t>
+          <t>4/16</t>
         </is>
       </c>
     </row>
@@ -6916,7 +6932,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6965,12 +6981,12 @@
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>11/16</t>
+          <t>2/16</t>
         </is>
       </c>
     </row>
@@ -7031,7 +7047,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7085,7 +7101,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>6/16</t>
+          <t>7/16</t>
         </is>
       </c>
     </row>
@@ -7093,22 +7109,22 @@
       <c r="A57" s="2" t="inlineStr"/>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A35591D</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
-        <is>
-          <t>15:20</t>
-        </is>
-      </c>
-      <c r="E57" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -7141,12 +7157,12 @@
       <c r="M57" s="2" t="inlineStr"/>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:50</t>
         </is>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7160,47 +7176,737 @@
       <c r="T57" s="2" t="inlineStr"/>
       <c r="U57" s="2" t="inlineStr">
         <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W57" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y57" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z57" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB57" s="2" t="inlineStr">
+        <is>
+          <t>80.7</t>
+        </is>
+      </c>
+      <c r="AC57" s="2" t="inlineStr">
+        <is>
+          <t>9/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr"/>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
           <t>15:20</t>
         </is>
       </c>
-      <c r="V57" s="2" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr"/>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr"/>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr"/>
+      <c r="R58" s="2" t="inlineStr"/>
+      <c r="S58" s="2" t="inlineStr"/>
+      <c r="T58" s="2" t="inlineStr"/>
+      <c r="U58" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="V58" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W57" s="2" t="inlineStr">
+      <c r="W58" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X57" s="2" t="inlineStr">
+      <c r="X58" s="2" t="inlineStr">
         <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Y57" s="2" t="inlineStr">
+      <c r="Y58" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z57" s="2" t="inlineStr">
+      <c r="Z58" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA57" s="2" t="inlineStr">
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
+          <t>85.7</t>
+        </is>
+      </c>
+      <c r="AC58" s="2" t="inlineStr">
+        <is>
+          <t>15/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr"/>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>15:32</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr"/>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr"/>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr"/>
+      <c r="R59" s="2" t="inlineStr"/>
+      <c r="S59" s="2" t="inlineStr"/>
+      <c r="T59" s="2" t="inlineStr"/>
+      <c r="U59" s="2" t="inlineStr">
+        <is>
+          <t>15:32</t>
+        </is>
+      </c>
+      <c r="V59" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W59" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y59" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z59" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB59" s="2" t="inlineStr">
+        <is>
+          <t>78.3</t>
+        </is>
+      </c>
+      <c r="AC59" s="2" t="inlineStr">
+        <is>
+          <t>5/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr"/>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr"/>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr"/>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr"/>
+      <c r="R60" s="2" t="inlineStr"/>
+      <c r="S60" s="2" t="inlineStr"/>
+      <c r="T60" s="2" t="inlineStr"/>
+      <c r="U60" s="2" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W60" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z60" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB57" s="2" t="inlineStr">
-        <is>
-          <t>86.0</t>
-        </is>
-      </c>
-      <c r="AC57" s="2" t="inlineStr">
-        <is>
-          <t>14/16</t>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="AC60" s="2" t="inlineStr">
+        <is>
+          <t>12/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr"/>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>沪A53629D</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr"/>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr"/>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr"/>
+      <c r="R61" s="2" t="inlineStr"/>
+      <c r="S61" s="2" t="inlineStr"/>
+      <c r="T61" s="2" t="inlineStr"/>
+      <c r="U61" s="2" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="V61" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W61" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y61" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z61" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
+          <t>74.8</t>
+        </is>
+      </c>
+      <c r="AC61" s="2" t="inlineStr">
+        <is>
+          <t>1/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr"/>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr"/>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr"/>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr"/>
+      <c r="R62" s="2" t="inlineStr"/>
+      <c r="S62" s="2" t="inlineStr"/>
+      <c r="T62" s="2" t="inlineStr"/>
+      <c r="U62" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="V62" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W62" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z62" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
+          <t>81.3</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="inlineStr">
+        <is>
+          <t>11/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr"/>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr"/>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr"/>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr"/>
+      <c r="R63" s="2" t="inlineStr"/>
+      <c r="S63" s="2" t="inlineStr"/>
+      <c r="T63" s="2" t="inlineStr"/>
+      <c r="U63" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="V63" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W63" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y63" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z63" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
+          <t>80.8</t>
+        </is>
+      </c>
+      <c r="AC63" s="2" t="inlineStr">
+        <is>
+          <t>10/16</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-02-浦东78路.xlsx
+++ b/data/export/2026-10-02-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC63"/>
+  <dimension ref="A1:AC71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>5/16</t>
+          <t>6/16</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,22 +827,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>7/16</t>
+          <t>4/16</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,7 +946,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>2/16</t>
+          <t>5/16</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1070,12 +1070,12 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>85.7</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1185,17 +1185,17 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>2/16</t>
+          <t>3/16</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1418,22 +1418,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>4/16</t>
+          <t>2/16</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1537,7 +1537,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>5/16</t>
+          <t>6/16</t>
         </is>
       </c>
     </row>
@@ -1617,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1780,12 +1780,12 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1894,22 +1894,22 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>7/16</t>
+          <t>4/16</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2013,7 +2013,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>2/16</t>
+          <t>5/16</t>
         </is>
       </c>
     </row>
@@ -2093,7 +2093,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2132,22 +2132,22 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>9/16</t>
+          <t>10/16</t>
         </is>
       </c>
     </row>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>85.7</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
@@ -2327,7 +2327,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2371,17 +2371,17 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>2/16</t>
+          <t>3/16</t>
         </is>
       </c>
     </row>
@@ -2557,7 +2557,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2676,7 +2676,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2730,7 +2730,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>5/16</t>
+          <t>6/16</t>
         </is>
       </c>
     </row>
@@ -2795,7 +2795,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2834,7 +2834,7 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2968,7 +2968,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>10/16</t>
+          <t>9/16</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3072,22 +3072,22 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA22" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>4/16</t>
+          <t>2/16</t>
         </is>
       </c>
     </row>
@@ -3148,7 +3148,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3263,7 +3263,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3302,7 +3302,7 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
@@ -3317,7 +3317,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>5/16</t>
+          <t>6/16</t>
         </is>
       </c>
     </row>
@@ -3378,7 +3378,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3417,22 +3417,22 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>7/16</t>
+          <t>4/16</t>
         </is>
       </c>
     </row>
@@ -3497,7 +3497,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3541,12 +3541,12 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
@@ -3616,7 +3616,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>85.7</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
@@ -3735,7 +3735,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3774,7 +3774,7 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -3789,7 +3789,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>2/16</t>
+          <t>5/16</t>
         </is>
       </c>
     </row>
@@ -3854,7 +3854,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3973,7 +3973,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4012,22 +4012,22 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA30" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>9/16</t>
+          <t>10/16</t>
         </is>
       </c>
     </row>
@@ -4092,7 +4092,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>10/16</t>
+          <t>9/16</t>
         </is>
       </c>
     </row>
@@ -4211,7 +4211,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4250,7 +4250,7 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
@@ -4265,7 +4265,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>5/16</t>
+          <t>6/16</t>
         </is>
       </c>
     </row>
@@ -4330,7 +4330,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4369,7 +4369,7 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
@@ -4384,7 +4384,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>5/16</t>
+          <t>6/16</t>
         </is>
       </c>
     </row>
@@ -4449,7 +4449,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4488,7 +4488,7 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
@@ -4568,7 +4568,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4612,12 +4612,12 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
@@ -4687,7 +4687,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4726,22 +4726,22 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA36" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>4/16</t>
+          <t>2/16</t>
         </is>
       </c>
     </row>
@@ -4802,7 +4802,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4841,7 +4841,7 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
@@ -4856,7 +4856,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>2/16</t>
+          <t>5/16</t>
         </is>
       </c>
     </row>
@@ -4921,7 +4921,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4960,22 +4960,22 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA38" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>9/16</t>
+          <t>10/16</t>
         </is>
       </c>
     </row>
@@ -5040,7 +5040,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5079,22 +5079,22 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>7/16</t>
+          <t>4/16</t>
         </is>
       </c>
     </row>
@@ -5159,7 +5159,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
@@ -5213,7 +5213,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>5/16</t>
+          <t>6/16</t>
         </is>
       </c>
     </row>
@@ -5278,7 +5278,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5397,7 +5397,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5436,7 +5436,7 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
@@ -5516,7 +5516,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5570,7 +5570,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>10/16</t>
+          <t>9/16</t>
         </is>
       </c>
     </row>
@@ -5635,7 +5635,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5674,22 +5674,22 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA44" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>4/16</t>
+          <t>2/16</t>
         </is>
       </c>
     </row>
@@ -5754,7 +5754,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5793,22 +5793,22 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA45" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>12/16</t>
+          <t>14/16</t>
         </is>
       </c>
     </row>
@@ -5873,7 +5873,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5912,22 +5912,22 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>7/16</t>
+          <t>4/16</t>
         </is>
       </c>
     </row>
@@ -5992,7 +5992,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6036,17 +6036,17 @@
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>2/16</t>
+          <t>3/16</t>
         </is>
       </c>
     </row>
@@ -6111,7 +6111,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6230,7 +6230,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6274,12 +6274,12 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>85.7</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
@@ -6349,7 +6349,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6403,7 +6403,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>10/16</t>
+          <t>9/16</t>
         </is>
       </c>
     </row>
@@ -6468,7 +6468,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6560,24 +6560,24 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>84分钟</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6587,7 +6587,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6626,22 +6626,22 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA52" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>12/16</t>
+          <t>14/16</t>
         </is>
       </c>
     </row>
@@ -6669,32 +6669,36 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M53" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
           <t>07:10</t>
@@ -6702,7 +6706,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6726,17 +6730,17 @@
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y53" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z53" s="2" t="inlineStr">
@@ -6746,12 +6750,12 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
@@ -6784,32 +6788,36 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M54" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -6817,7 +6825,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6841,37 +6849,37 @@
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y54" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA54" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>4/16</t>
+          <t>2/16</t>
         </is>
       </c>
     </row>
@@ -6899,32 +6907,36 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr"/>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M55" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -6932,7 +6944,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6956,17 +6968,17 @@
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y55" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z55" s="2" t="inlineStr">
@@ -6976,17 +6988,17 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>2/16</t>
+          <t>3/16</t>
         </is>
       </c>
     </row>
@@ -7014,32 +7026,36 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr"/>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M56" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -7047,7 +7063,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7071,37 +7087,37 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y56" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>7/16</t>
+          <t>4/16</t>
         </is>
       </c>
     </row>
@@ -7129,32 +7145,36 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr"/>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M57" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
           <t>07:50</t>
@@ -7162,7 +7182,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7186,37 +7206,37 @@
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y57" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA57" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>9/16</t>
+          <t>10/16</t>
         </is>
       </c>
     </row>
@@ -7244,32 +7264,36 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M58" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -7277,7 +7301,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7301,17 +7325,17 @@
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y58" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z58" s="2" t="inlineStr">
@@ -7321,12 +7345,12 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>85.7</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
@@ -7392,7 +7416,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7431,7 +7455,7 @@
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA59" s="2" t="inlineStr">
@@ -7446,7 +7470,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>5/16</t>
+          <t>6/16</t>
         </is>
       </c>
     </row>
@@ -7507,7 +7531,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7622,7 +7646,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7737,7 +7761,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7781,12 +7805,12 @@
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
@@ -7852,7 +7876,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7906,7 +7930,927 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
+          <t>9/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr"/>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr"/>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr"/>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr"/>
+      <c r="R64" s="2" t="inlineStr"/>
+      <c r="S64" s="2" t="inlineStr"/>
+      <c r="T64" s="2" t="inlineStr"/>
+      <c r="U64" s="2" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="V64" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W64" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y64" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z64" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
+          <t>80.3</t>
+        </is>
+      </c>
+      <c r="AC64" s="2" t="inlineStr">
+        <is>
+          <t>8/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr"/>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr"/>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr"/>
+      <c r="N65" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr"/>
+      <c r="R65" s="2" t="inlineStr"/>
+      <c r="S65" s="2" t="inlineStr"/>
+      <c r="T65" s="2" t="inlineStr"/>
+      <c r="U65" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="V65" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W65" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y65" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z65" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
+      <c r="AC65" s="2" t="inlineStr">
+        <is>
+          <t>2/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr"/>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr"/>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr"/>
+      <c r="N66" s="2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr"/>
+      <c r="R66" s="2" t="inlineStr"/>
+      <c r="S66" s="2" t="inlineStr"/>
+      <c r="T66" s="2" t="inlineStr"/>
+      <c r="U66" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="V66" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W66" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y66" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z66" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB66" s="2" t="inlineStr">
+        <is>
+          <t>84.5</t>
+        </is>
+      </c>
+      <c r="AC66" s="2" t="inlineStr">
+        <is>
+          <t>14/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr"/>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr"/>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr"/>
+      <c r="N67" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr"/>
+      <c r="R67" s="2" t="inlineStr"/>
+      <c r="S67" s="2" t="inlineStr"/>
+      <c r="T67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W67" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z67" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
+          <t>77.8</t>
+        </is>
+      </c>
+      <c r="AC67" s="2" t="inlineStr">
+        <is>
+          <t>4/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr"/>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr"/>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr"/>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr"/>
+      <c r="R68" s="2" t="inlineStr"/>
+      <c r="S68" s="2" t="inlineStr"/>
+      <c r="T68" s="2" t="inlineStr"/>
+      <c r="U68" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="V68" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W68" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y68" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z68" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
+          <t>78.0</t>
+        </is>
+      </c>
+      <c r="AC68" s="2" t="inlineStr">
+        <is>
+          <t>5/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr"/>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr"/>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr"/>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr"/>
+      <c r="R69" s="2" t="inlineStr"/>
+      <c r="S69" s="2" t="inlineStr"/>
+      <c r="T69" s="2" t="inlineStr"/>
+      <c r="U69" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="V69" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W69" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y69" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z69" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB69" s="2" t="inlineStr">
+        <is>
+          <t>78.3</t>
+        </is>
+      </c>
+      <c r="AC69" s="2" t="inlineStr">
+        <is>
+          <t>6/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr"/>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr"/>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr"/>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>07:50</t>
+        </is>
+      </c>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr"/>
+      <c r="R70" s="2" t="inlineStr"/>
+      <c r="S70" s="2" t="inlineStr"/>
+      <c r="T70" s="2" t="inlineStr"/>
+      <c r="U70" s="2" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="V70" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W70" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z70" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AC70" s="2" t="inlineStr">
+        <is>
           <t>10/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr"/>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr"/>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr"/>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr"/>
+      <c r="R71" s="2" t="inlineStr"/>
+      <c r="S71" s="2" t="inlineStr"/>
+      <c r="T71" s="2" t="inlineStr"/>
+      <c r="U71" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="V71" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W71" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z71" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr">
+        <is>
+          <t>78.3</t>
+        </is>
+      </c>
+      <c r="AC71" s="2" t="inlineStr">
+        <is>
+          <t>6/16</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-02-浦东78路.xlsx
+++ b/data/export/2026-10-02-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC71"/>
+  <dimension ref="A1:AC80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1075,7 +1075,7 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1180,7 +1180,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>3/16</t>
+          <t>2/16</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1418,22 +1418,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>77.7</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>2/16</t>
+          <t>3/16</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1656,22 +1656,22 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>84.3</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>12/16</t>
+          <t>13/16</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1775,22 +1775,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>82.2</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>11/16</t>
+          <t>10/16</t>
         </is>
       </c>
     </row>
@@ -1855,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2093,7 +2093,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2147,7 +2147,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>10/16</t>
+          <t>11/16</t>
         </is>
       </c>
     </row>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2247,7 +2247,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
@@ -2327,7 +2327,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2366,7 +2366,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2381,7 +2381,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>3/16</t>
+          <t>2/16</t>
         </is>
       </c>
     </row>
@@ -2557,7 +2557,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
@@ -2676,7 +2676,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2720,17 +2720,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>6/16</t>
+          <t>7/16</t>
         </is>
       </c>
     </row>
@@ -2795,7 +2795,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2834,17 +2834,17 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2953,17 +2953,17 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
@@ -3033,7 +3033,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3072,22 +3072,22 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA22" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>77.7</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>2/16</t>
+          <t>3/16</t>
         </is>
       </c>
     </row>
@@ -3148,7 +3148,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3187,22 +3187,22 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>84.3</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>12/16</t>
+          <t>13/16</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3378,7 +3378,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3497,7 +3497,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3536,22 +3536,22 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA26" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>82.2</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>11/16</t>
+          <t>10/16</t>
         </is>
       </c>
     </row>
@@ -3616,7 +3616,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3655,7 +3655,7 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
@@ -3665,7 +3665,7 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
@@ -3735,7 +3735,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3854,7 +3854,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3893,7 +3893,7 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
@@ -3973,7 +3973,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4027,7 +4027,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>10/16</t>
+          <t>11/16</t>
         </is>
       </c>
     </row>
@@ -4092,7 +4092,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4131,17 +4131,17 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA31" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
@@ -4211,7 +4211,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4255,17 +4255,17 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>6/16</t>
+          <t>7/16</t>
         </is>
       </c>
     </row>
@@ -4330,7 +4330,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4449,7 +4449,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4488,17 +4488,17 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA34" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
@@ -4568,7 +4568,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4607,22 +4607,22 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA35" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>82.2</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>11/16</t>
+          <t>10/16</t>
         </is>
       </c>
     </row>
@@ -4687,7 +4687,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4726,22 +4726,22 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA36" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>77.7</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>2/16</t>
+          <t>3/16</t>
         </is>
       </c>
     </row>
@@ -4802,7 +4802,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4921,7 +4921,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4975,7 +4975,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>10/16</t>
+          <t>11/16</t>
         </is>
       </c>
     </row>
@@ -5040,7 +5040,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5159,7 +5159,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5203,17 +5203,17 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>6/16</t>
+          <t>7/16</t>
         </is>
       </c>
     </row>
@@ -5278,7 +5278,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5317,7 +5317,7 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
@@ -5397,7 +5397,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5436,17 +5436,17 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA42" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
@@ -5516,7 +5516,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5555,17 +5555,17 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA43" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
@@ -5635,7 +5635,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5674,22 +5674,22 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA44" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>77.7</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>2/16</t>
+          <t>3/16</t>
         </is>
       </c>
     </row>
@@ -5754,7 +5754,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5793,7 +5793,7 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
@@ -5873,7 +5873,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5992,7 +5992,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6031,7 +6031,7 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
@@ -6046,7 +6046,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>3/16</t>
+          <t>2/16</t>
         </is>
       </c>
     </row>
@@ -6111,7 +6111,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6150,7 +6150,7 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
@@ -6230,7 +6230,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA49" s="2" t="inlineStr">
@@ -6279,7 +6279,7 @@
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
@@ -6349,7 +6349,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6388,17 +6388,17 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA50" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
@@ -6468,7 +6468,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6507,22 +6507,22 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>84.3</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>12/16</t>
+          <t>13/16</t>
         </is>
       </c>
     </row>
@@ -6587,7 +6587,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6626,7 +6626,7 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA52" s="2" t="inlineStr">
@@ -6706,7 +6706,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6745,22 +6745,22 @@
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA53" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>82.2</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>11/16</t>
+          <t>10/16</t>
         </is>
       </c>
     </row>
@@ -6825,7 +6825,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6864,22 +6864,22 @@
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA54" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>77.7</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>2/16</t>
+          <t>3/16</t>
         </is>
       </c>
     </row>
@@ -6944,7 +6944,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6983,7 +6983,7 @@
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA55" s="2" t="inlineStr">
@@ -6998,7 +6998,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>3/16</t>
+          <t>2/16</t>
         </is>
       </c>
     </row>
@@ -7063,7 +7063,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7182,7 +7182,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7236,7 +7236,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>10/16</t>
+          <t>11/16</t>
         </is>
       </c>
     </row>
@@ -7274,24 +7274,24 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>85分钟</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -7301,7 +7301,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7340,7 +7340,7 @@
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
@@ -7350,7 +7350,7 @@
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
@@ -7383,32 +7383,36 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:53</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr"/>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M59" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
           <t>08:20</t>
@@ -7416,7 +7420,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7440,17 +7444,17 @@
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y59" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z59" s="2" t="inlineStr">
@@ -7460,17 +7464,17 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>6/16</t>
+          <t>7/16</t>
         </is>
       </c>
     </row>
@@ -7498,32 +7502,36 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M60" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -7531,7 +7539,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7555,37 +7563,37 @@
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y60" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>84.3</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>12/16</t>
+          <t>13/16</t>
         </is>
       </c>
     </row>
@@ -7646,7 +7654,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7685,7 +7693,7 @@
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA61" s="2" t="inlineStr">
@@ -7728,32 +7736,36 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M62" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
           <t>07:10</t>
@@ -7761,7 +7773,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7785,37 +7797,37 @@
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y62" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA62" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>82.2</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>11/16</t>
+          <t>10/16</t>
         </is>
       </c>
     </row>
@@ -7843,32 +7855,36 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M63" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
           <t>08:20</t>
@@ -7876,7 +7892,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7900,32 +7916,32 @@
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y63" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA63" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
@@ -7958,32 +7974,36 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M64" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
           <t>08:40</t>
@@ -7991,7 +8011,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8015,32 +8035,32 @@
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y64" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z64" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA64" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
@@ -8073,32 +8093,36 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr"/>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M65" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -8106,7 +8130,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8130,37 +8154,37 @@
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y65" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z65" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA65" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>77.7</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>2/16</t>
+          <t>3/16</t>
         </is>
       </c>
     </row>
@@ -8221,7 +8245,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8260,7 +8284,7 @@
       </c>
       <c r="Z66" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA66" s="2" t="inlineStr">
@@ -8336,7 +8360,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8451,7 +8475,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8566,7 +8590,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8681,7 +8705,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8735,7 +8759,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>10/16</t>
+          <t>11/16</t>
         </is>
       </c>
     </row>
@@ -8743,22 +8767,22 @@
       <c r="A71" s="2" t="inlineStr"/>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>沪A56123D</t>
+          <t>沪A36809D</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="E71" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
@@ -8791,12 +8815,12 @@
       <c r="M71" s="2" t="inlineStr"/>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8810,47 +8834,1082 @@
       <c r="T71" s="2" t="inlineStr"/>
       <c r="U71" s="2" t="inlineStr">
         <is>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="V71" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W71" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z71" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr">
+        <is>
+          <t>77.3</t>
+        </is>
+      </c>
+      <c r="AC71" s="2" t="inlineStr">
+        <is>
+          <t>2/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr"/>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
           <t>17:00</t>
         </is>
       </c>
-      <c r="V71" s="2" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr"/>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr"/>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr"/>
+      <c r="R72" s="2" t="inlineStr"/>
+      <c r="S72" s="2" t="inlineStr"/>
+      <c r="T72" s="2" t="inlineStr"/>
+      <c r="U72" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="V72" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W71" s="2" t="inlineStr">
+      <c r="W72" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X71" s="2" t="inlineStr">
+      <c r="X72" s="2" t="inlineStr">
         <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Y71" s="2" t="inlineStr">
+      <c r="Y72" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z71" s="2" t="inlineStr">
+      <c r="Z72" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA71" s="2" t="inlineStr">
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
+      <c r="AC72" s="2" t="inlineStr">
+        <is>
+          <t>7/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr"/>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>17:10</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr"/>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr"/>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q73" s="2" t="inlineStr"/>
+      <c r="R73" s="2" t="inlineStr"/>
+      <c r="S73" s="2" t="inlineStr"/>
+      <c r="T73" s="2" t="inlineStr"/>
+      <c r="U73" s="2" t="inlineStr">
+        <is>
+          <t>17:10</t>
+        </is>
+      </c>
+      <c r="V73" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W73" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z73" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="AC73" s="2" t="inlineStr">
+        <is>
+          <t>15/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr"/>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>沪A53629D</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr"/>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr"/>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr"/>
+      <c r="R74" s="2" t="inlineStr"/>
+      <c r="S74" s="2" t="inlineStr"/>
+      <c r="T74" s="2" t="inlineStr"/>
+      <c r="U74" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="V74" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W74" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y74" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z74" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr">
+        <is>
+          <t>74.8</t>
+        </is>
+      </c>
+      <c r="AC74" s="2" t="inlineStr">
+        <is>
+          <t>1/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr"/>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr"/>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr"/>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr"/>
+      <c r="R75" s="2" t="inlineStr"/>
+      <c r="S75" s="2" t="inlineStr"/>
+      <c r="T75" s="2" t="inlineStr"/>
+      <c r="U75" s="2" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="V75" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W75" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y75" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z75" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AB71" s="2" t="inlineStr">
-        <is>
-          <t>78.3</t>
-        </is>
-      </c>
-      <c r="AC71" s="2" t="inlineStr">
-        <is>
-          <t>6/16</t>
+      <c r="AB75" s="2" t="inlineStr">
+        <is>
+          <t>84.3</t>
+        </is>
+      </c>
+      <c r="AC75" s="2" t="inlineStr">
+        <is>
+          <t>13/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr"/>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr"/>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr"/>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr"/>
+      <c r="R76" s="2" t="inlineStr"/>
+      <c r="S76" s="2" t="inlineStr"/>
+      <c r="T76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="V76" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W76" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y76" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z76" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB76" s="2" t="inlineStr">
+        <is>
+          <t>80.4</t>
+        </is>
+      </c>
+      <c r="AC76" s="2" t="inlineStr">
+        <is>
+          <t>9/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr"/>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>17:42</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr"/>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr"/>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr"/>
+      <c r="R77" s="2" t="inlineStr"/>
+      <c r="S77" s="2" t="inlineStr"/>
+      <c r="T77" s="2" t="inlineStr"/>
+      <c r="U77" s="2" t="inlineStr">
+        <is>
+          <t>17:42</t>
+        </is>
+      </c>
+      <c r="V77" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W77" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y77" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z77" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB77" s="2" t="inlineStr">
+        <is>
+          <t>80.2</t>
+        </is>
+      </c>
+      <c r="AC77" s="2" t="inlineStr">
+        <is>
+          <t>8/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr"/>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>17:42</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr"/>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr"/>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr"/>
+      <c r="R78" s="2" t="inlineStr"/>
+      <c r="S78" s="2" t="inlineStr"/>
+      <c r="T78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="inlineStr">
+        <is>
+          <t>17:42</t>
+        </is>
+      </c>
+      <c r="V78" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W78" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y78" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z78" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB78" s="2" t="inlineStr">
+        <is>
+          <t>81.8</t>
+        </is>
+      </c>
+      <c r="AC78" s="2" t="inlineStr">
+        <is>
+          <t>10/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr"/>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr"/>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr"/>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr"/>
+      <c r="R79" s="2" t="inlineStr"/>
+      <c r="S79" s="2" t="inlineStr"/>
+      <c r="T79" s="2" t="inlineStr"/>
+      <c r="U79" s="2" t="inlineStr">
+        <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="V79" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W79" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y79" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z79" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB79" s="2" t="inlineStr">
+        <is>
+          <t>84.5</t>
+        </is>
+      </c>
+      <c r="AC79" s="2" t="inlineStr">
+        <is>
+          <t>14/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr"/>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr"/>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr"/>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr"/>
+      <c r="R80" s="2" t="inlineStr"/>
+      <c r="S80" s="2" t="inlineStr"/>
+      <c r="T80" s="2" t="inlineStr"/>
+      <c r="U80" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="V80" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W80" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y80" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z80" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB80" s="2" t="inlineStr">
+        <is>
+          <t>77.7</t>
+        </is>
+      </c>
+      <c r="AC80" s="2" t="inlineStr">
+        <is>
+          <t>3/16</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-02-浦东78路.xlsx
+++ b/data/export/2026-10-02-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC80"/>
+  <dimension ref="A1:AC89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,22 +708,22 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>6/16</t>
+          <t>7/16</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,22 +827,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>4/16</t>
+          <t>6/16</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,22 +946,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>5/16</t>
+          <t>3/16</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1180,22 +1180,22 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>2/16</t>
+          <t>3/16</t>
         </is>
       </c>
     </row>
@@ -1314,7 +1314,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>12/16</t>
+          <t>13/16</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>3/16</t>
+          <t>2/16</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1537,22 +1537,22 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>6/16</t>
+          <t>7/16</t>
         </is>
       </c>
     </row>
@@ -1617,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1671,7 +1671,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>13/16</t>
+          <t>14/16</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1894,22 +1894,22 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>4/16</t>
+          <t>6/16</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2013,22 +2013,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>5/16</t>
+          <t>3/16</t>
         </is>
       </c>
     </row>
@@ -2093,7 +2093,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2132,17 +2132,17 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
@@ -2208,7 +2208,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2247,7 +2247,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2327,7 +2327,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2366,22 +2366,22 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>2/16</t>
+          <t>3/16</t>
         </is>
       </c>
     </row>
@@ -2557,7 +2557,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2596,17 +2596,17 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
@@ -2676,7 +2676,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2715,22 +2715,22 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA19" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>7/16</t>
+          <t>5/16</t>
         </is>
       </c>
     </row>
@@ -2795,7 +2795,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3033,7 +3033,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3082,12 +3082,12 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>3/16</t>
+          <t>2/16</t>
         </is>
       </c>
     </row>
@@ -3148,7 +3148,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3187,7 +3187,7 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
@@ -3202,7 +3202,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>13/16</t>
+          <t>14/16</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3302,22 +3302,22 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>6/16</t>
+          <t>7/16</t>
         </is>
       </c>
     </row>
@@ -3378,7 +3378,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3417,22 +3417,22 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>4/16</t>
+          <t>6/16</t>
         </is>
       </c>
     </row>
@@ -3497,7 +3497,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3616,7 +3616,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3655,7 +3655,7 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
@@ -3735,7 +3735,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3774,22 +3774,22 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>5/16</t>
+          <t>3/16</t>
         </is>
       </c>
     </row>
@@ -3854,7 +3854,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3893,17 +3893,17 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
@@ -3973,7 +3973,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4012,17 +4012,17 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA30" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
@@ -4092,7 +4092,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4211,7 +4211,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4250,22 +4250,22 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA32" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>7/16</t>
+          <t>5/16</t>
         </is>
       </c>
     </row>
@@ -4330,7 +4330,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4369,22 +4369,22 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>6/16</t>
+          <t>7/16</t>
         </is>
       </c>
     </row>
@@ -4449,7 +4449,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4568,7 +4568,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4687,7 +4687,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4736,12 +4736,12 @@
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>3/16</t>
+          <t>2/16</t>
         </is>
       </c>
     </row>
@@ -4802,7 +4802,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4841,22 +4841,22 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>5/16</t>
+          <t>3/16</t>
         </is>
       </c>
     </row>
@@ -4921,7 +4921,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4960,17 +4960,17 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA38" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
@@ -5040,7 +5040,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5079,22 +5079,22 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>4/16</t>
+          <t>6/16</t>
         </is>
       </c>
     </row>
@@ -5159,7 +5159,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5198,22 +5198,22 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA40" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>7/16</t>
+          <t>5/16</t>
         </is>
       </c>
     </row>
@@ -5278,7 +5278,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5317,17 +5317,17 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
@@ -5397,7 +5397,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5516,7 +5516,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5635,7 +5635,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5684,12 +5684,12 @@
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>3/16</t>
+          <t>2/16</t>
         </is>
       </c>
     </row>
@@ -5754,7 +5754,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5798,17 +5798,17 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>14/16</t>
+          <t>12/16</t>
         </is>
       </c>
     </row>
@@ -5873,7 +5873,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5912,22 +5912,22 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>4/16</t>
+          <t>6/16</t>
         </is>
       </c>
     </row>
@@ -5992,7 +5992,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6031,22 +6031,22 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>2/16</t>
+          <t>3/16</t>
         </is>
       </c>
     </row>
@@ -6111,7 +6111,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6150,17 +6150,17 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
@@ -6230,7 +6230,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA49" s="2" t="inlineStr">
@@ -6349,7 +6349,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6468,7 +6468,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6507,7 +6507,7 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA51" s="2" t="inlineStr">
@@ -6522,7 +6522,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>13/16</t>
+          <t>14/16</t>
         </is>
       </c>
     </row>
@@ -6587,7 +6587,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6631,17 +6631,17 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>14/16</t>
+          <t>12/16</t>
         </is>
       </c>
     </row>
@@ -6706,7 +6706,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>3/16</t>
+          <t>2/16</t>
         </is>
       </c>
     </row>
@@ -6944,7 +6944,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6983,22 +6983,22 @@
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>2/16</t>
+          <t>3/16</t>
         </is>
       </c>
     </row>
@@ -7063,7 +7063,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7102,22 +7102,22 @@
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>4/16</t>
+          <t>6/16</t>
         </is>
       </c>
     </row>
@@ -7182,7 +7182,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7221,17 +7221,17 @@
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA57" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
@@ -7301,7 +7301,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7340,7 +7340,7 @@
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
@@ -7420,7 +7420,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7459,22 +7459,22 @@
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA59" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>7/16</t>
+          <t>5/16</t>
         </is>
       </c>
     </row>
@@ -7539,7 +7539,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7578,7 +7578,7 @@
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA60" s="2" t="inlineStr">
@@ -7593,7 +7593,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>13/16</t>
+          <t>14/16</t>
         </is>
       </c>
     </row>
@@ -7654,7 +7654,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7693,17 +7693,17 @@
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
@@ -7773,7 +7773,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7892,7 +7892,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -8011,7 +8011,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8103,24 +8103,24 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr"/>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -8130,7 +8130,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8179,12 +8179,12 @@
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>3/16</t>
+          <t>2/16</t>
         </is>
       </c>
     </row>
@@ -8212,32 +8212,36 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M66" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
           <t>12:00</t>
@@ -8245,7 +8249,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8269,17 +8273,17 @@
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y66" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z66" s="2" t="inlineStr">
@@ -8289,17 +8293,17 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>14/16</t>
+          <t>12/16</t>
         </is>
       </c>
     </row>
@@ -8327,32 +8331,36 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr"/>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M67" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -8360,7 +8368,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8384,37 +8392,37 @@
       </c>
       <c r="W67" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y67" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z67" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>4/16</t>
+          <t>6/16</t>
         </is>
       </c>
     </row>
@@ -8442,32 +8450,36 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M68" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -8475,7 +8487,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8499,37 +8511,37 @@
       </c>
       <c r="W68" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y68" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z68" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>5/16</t>
+          <t>3/16</t>
         </is>
       </c>
     </row>
@@ -8557,32 +8569,36 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr"/>
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M69" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -8590,7 +8606,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8614,37 +8630,37 @@
       </c>
       <c r="W69" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y69" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z69" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>6/16</t>
+          <t>7/16</t>
         </is>
       </c>
     </row>
@@ -8672,32 +8688,36 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M70" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
           <t>07:50</t>
@@ -8705,7 +8725,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8729,32 +8749,32 @@
       </c>
       <c r="W70" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y70" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z70" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA70" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
@@ -8787,32 +8807,36 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr"/>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M71" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -8820,7 +8844,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8844,37 +8868,37 @@
       </c>
       <c r="W71" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y71" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z71" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA71" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>2/16</t>
+          <t>3/16</t>
         </is>
       </c>
     </row>
@@ -8902,32 +8926,36 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M72" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
           <t>08:20</t>
@@ -8935,7 +8963,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -8959,37 +8987,37 @@
       </c>
       <c r="W72" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y72" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z72" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA72" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>7/16</t>
+          <t>5/16</t>
         </is>
       </c>
     </row>
@@ -9050,7 +9078,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9089,7 +9117,7 @@
       </c>
       <c r="Z73" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA73" s="2" t="inlineStr">
@@ -9132,32 +9160,36 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr"/>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M74" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
           <t>08:20</t>
@@ -9165,7 +9197,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9189,32 +9221,32 @@
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y74" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z74" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
@@ -9280,7 +9312,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9319,7 +9351,7 @@
       </c>
       <c r="Z75" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA75" s="2" t="inlineStr">
@@ -9334,7 +9366,7 @@
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>13/16</t>
+          <t>14/16</t>
         </is>
       </c>
     </row>
@@ -9395,7 +9427,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9510,7 +9542,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9625,7 +9657,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9740,7 +9772,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9784,17 +9816,17 @@
       </c>
       <c r="AA79" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>14/16</t>
+          <t>12/16</t>
         </is>
       </c>
     </row>
@@ -9855,7 +9887,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9904,12 +9936,1047 @@
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
+          <t>2/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr"/>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr"/>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr"/>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr"/>
+      <c r="R81" s="2" t="inlineStr"/>
+      <c r="S81" s="2" t="inlineStr"/>
+      <c r="T81" s="2" t="inlineStr"/>
+      <c r="U81" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="V81" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W81" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y81" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z81" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB81" s="2" t="inlineStr">
+        <is>
+          <t>77.2</t>
+        </is>
+      </c>
+      <c r="AC81" s="2" t="inlineStr">
+        <is>
           <t>3/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr"/>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr"/>
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr"/>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q82" s="2" t="inlineStr"/>
+      <c r="R82" s="2" t="inlineStr"/>
+      <c r="S82" s="2" t="inlineStr"/>
+      <c r="T82" s="2" t="inlineStr"/>
+      <c r="U82" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="V82" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W82" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y82" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z82" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB82" s="2" t="inlineStr">
+        <is>
+          <t>78.8</t>
+        </is>
+      </c>
+      <c r="AC82" s="2" t="inlineStr">
+        <is>
+          <t>6/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr"/>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr"/>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr"/>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q83" s="2" t="inlineStr"/>
+      <c r="R83" s="2" t="inlineStr"/>
+      <c r="S83" s="2" t="inlineStr"/>
+      <c r="T83" s="2" t="inlineStr"/>
+      <c r="U83" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="V83" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W83" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y83" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z83" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB83" s="2" t="inlineStr">
+        <is>
+          <t>79.5</t>
+        </is>
+      </c>
+      <c r="AC83" s="2" t="inlineStr">
+        <is>
+          <t>7/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr"/>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr"/>
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr"/>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>07:50</t>
+        </is>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q84" s="2" t="inlineStr"/>
+      <c r="R84" s="2" t="inlineStr"/>
+      <c r="S84" s="2" t="inlineStr"/>
+      <c r="T84" s="2" t="inlineStr"/>
+      <c r="U84" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="V84" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W84" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y84" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z84" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA84" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB84" s="2" t="inlineStr">
+        <is>
+          <t>82.8</t>
+        </is>
+      </c>
+      <c r="AC84" s="2" t="inlineStr">
+        <is>
+          <t>11/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr"/>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr"/>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr"/>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q85" s="2" t="inlineStr"/>
+      <c r="R85" s="2" t="inlineStr"/>
+      <c r="S85" s="2" t="inlineStr"/>
+      <c r="T85" s="2" t="inlineStr"/>
+      <c r="U85" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="V85" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W85" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y85" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z85" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA85" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB85" s="2" t="inlineStr">
+        <is>
+          <t>77.2</t>
+        </is>
+      </c>
+      <c r="AC85" s="2" t="inlineStr">
+        <is>
+          <t>3/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr"/>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr"/>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr"/>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q86" s="2" t="inlineStr"/>
+      <c r="R86" s="2" t="inlineStr"/>
+      <c r="S86" s="2" t="inlineStr"/>
+      <c r="T86" s="2" t="inlineStr"/>
+      <c r="U86" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="V86" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W86" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y86" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z86" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA86" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB86" s="2" t="inlineStr">
+        <is>
+          <t>78.2</t>
+        </is>
+      </c>
+      <c r="AC86" s="2" t="inlineStr">
+        <is>
+          <t>5/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr"/>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr"/>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr"/>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q87" s="2" t="inlineStr"/>
+      <c r="R87" s="2" t="inlineStr"/>
+      <c r="S87" s="2" t="inlineStr"/>
+      <c r="T87" s="2" t="inlineStr"/>
+      <c r="U87" s="2" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="V87" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W87" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y87" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z87" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA87" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB87" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="AC87" s="2" t="inlineStr">
+        <is>
+          <t>15/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr"/>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>沪A53629D</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr"/>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr"/>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q88" s="2" t="inlineStr"/>
+      <c r="R88" s="2" t="inlineStr"/>
+      <c r="S88" s="2" t="inlineStr"/>
+      <c r="T88" s="2" t="inlineStr"/>
+      <c r="U88" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="V88" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W88" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y88" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z88" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA88" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB88" s="2" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="AC88" s="2" t="inlineStr">
+        <is>
+          <t>1/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr"/>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr"/>
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr"/>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P89" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q89" s="2" t="inlineStr"/>
+      <c r="R89" s="2" t="inlineStr"/>
+      <c r="S89" s="2" t="inlineStr"/>
+      <c r="T89" s="2" t="inlineStr"/>
+      <c r="U89" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="V89" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W89" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y89" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z89" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA89" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB89" s="2" t="inlineStr">
+        <is>
+          <t>84.3</t>
+        </is>
+      </c>
+      <c r="AC89" s="2" t="inlineStr">
+        <is>
+          <t>14/16</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-02-浦东78路.xlsx
+++ b/data/export/2026-10-02-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC89"/>
+  <dimension ref="A1:AC95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,22 +708,22 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>7/16</t>
+          <t>5/16</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>6/16</t>
+          <t>7/16</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,17 +946,17 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1070,12 +1070,12 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>3/16</t>
+          <t>4/16</t>
         </is>
       </c>
     </row>
@@ -1314,7 +1314,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>13/16</t>
+          <t>14/16</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1537,22 +1537,22 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>7/16</t>
+          <t>5/16</t>
         </is>
       </c>
     </row>
@@ -1617,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1661,17 +1661,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>84.3</t>
+          <t>83.2</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>14/16</t>
+          <t>13/16</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1775,22 +1775,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>10/16</t>
+          <t>9/16</t>
         </is>
       </c>
     </row>
@@ -1855,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1909,7 +1909,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>6/16</t>
+          <t>7/16</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2013,17 +2013,17 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
@@ -2093,7 +2093,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2132,22 +2132,22 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>83.2</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>11/16</t>
+          <t>12/16</t>
         </is>
       </c>
     </row>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
@@ -2327,7 +2327,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2381,7 +2381,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>3/16</t>
+          <t>4/16</t>
         </is>
       </c>
     </row>
@@ -2557,7 +2557,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2676,7 +2676,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2795,7 +2795,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2839,12 +2839,12 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2953,17 +2953,17 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>80.4</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
@@ -3033,7 +3033,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3077,12 +3077,12 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
@@ -3148,7 +3148,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3192,17 +3192,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>84.3</t>
+          <t>83.2</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>14/16</t>
+          <t>13/16</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3302,22 +3302,22 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>7/16</t>
+          <t>5/16</t>
         </is>
       </c>
     </row>
@@ -3378,7 +3378,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3432,7 +3432,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>6/16</t>
+          <t>7/16</t>
         </is>
       </c>
     </row>
@@ -3497,7 +3497,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3536,22 +3536,22 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA26" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>10/16</t>
+          <t>9/16</t>
         </is>
       </c>
     </row>
@@ -3616,7 +3616,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
@@ -3735,7 +3735,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3774,17 +3774,17 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
@@ -3854,7 +3854,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3973,7 +3973,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4012,22 +4012,22 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA30" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>83.2</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>11/16</t>
+          <t>12/16</t>
         </is>
       </c>
     </row>
@@ -4092,7 +4092,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4131,17 +4131,17 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA31" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>80.4</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
@@ -4211,7 +4211,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4250,7 +4250,7 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
@@ -4330,7 +4330,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4369,22 +4369,22 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>7/16</t>
+          <t>5/16</t>
         </is>
       </c>
     </row>
@@ -4449,7 +4449,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4493,12 +4493,12 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
@@ -4568,7 +4568,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4607,22 +4607,22 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA35" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>10/16</t>
+          <t>9/16</t>
         </is>
       </c>
     </row>
@@ -4687,7 +4687,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4731,12 +4731,12 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
@@ -4802,7 +4802,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4841,17 +4841,17 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
@@ -4921,7 +4921,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4960,22 +4960,22 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA38" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>83.2</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>11/16</t>
+          <t>12/16</t>
         </is>
       </c>
     </row>
@@ -5040,7 +5040,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5094,7 +5094,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>6/16</t>
+          <t>7/16</t>
         </is>
       </c>
     </row>
@@ -5159,7 +5159,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
@@ -5278,7 +5278,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5397,7 +5397,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
@@ -5516,7 +5516,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5555,17 +5555,17 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA43" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>80.4</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
@@ -5635,7 +5635,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5679,12 +5679,12 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5754,7 +5754,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5798,17 +5798,17 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>12/16</t>
+          <t>11/16</t>
         </is>
       </c>
     </row>
@@ -5873,7 +5873,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5927,7 +5927,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>6/16</t>
+          <t>7/16</t>
         </is>
       </c>
     </row>
@@ -5992,7 +5992,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6046,7 +6046,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>3/16</t>
+          <t>4/16</t>
         </is>
       </c>
     </row>
@@ -6111,7 +6111,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6230,7 +6230,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6274,12 +6274,12 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
@@ -6349,7 +6349,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6388,17 +6388,17 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA50" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>80.4</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
@@ -6468,7 +6468,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6512,17 +6512,17 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>84.3</t>
+          <t>83.2</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>14/16</t>
+          <t>13/16</t>
         </is>
       </c>
     </row>
@@ -6587,7 +6587,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6631,17 +6631,17 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>12/16</t>
+          <t>11/16</t>
         </is>
       </c>
     </row>
@@ -6706,7 +6706,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6745,22 +6745,22 @@
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA53" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>10/16</t>
+          <t>9/16</t>
         </is>
       </c>
     </row>
@@ -6825,7 +6825,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6869,12 +6869,12 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
@@ -6944,7 +6944,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6998,7 +6998,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>3/16</t>
+          <t>4/16</t>
         </is>
       </c>
     </row>
@@ -7063,7 +7063,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7117,7 +7117,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>6/16</t>
+          <t>7/16</t>
         </is>
       </c>
     </row>
@@ -7182,7 +7182,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7221,22 +7221,22 @@
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA57" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>83.2</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>11/16</t>
+          <t>12/16</t>
         </is>
       </c>
     </row>
@@ -7301,7 +7301,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
@@ -7420,7 +7420,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7459,7 +7459,7 @@
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA59" s="2" t="inlineStr">
@@ -7539,7 +7539,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7583,17 +7583,17 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>84.3</t>
+          <t>83.2</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>14/16</t>
+          <t>13/16</t>
         </is>
       </c>
     </row>
@@ -7654,7 +7654,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7773,7 +7773,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7812,22 +7812,22 @@
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA62" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>10/16</t>
+          <t>9/16</t>
         </is>
       </c>
     </row>
@@ -7892,7 +7892,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7931,17 +7931,17 @@
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA63" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>80.4</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
@@ -8011,7 +8011,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8055,12 +8055,12 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
@@ -8130,7 +8130,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8174,12 +8174,12 @@
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
@@ -8249,7 +8249,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8293,17 +8293,17 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>12/16</t>
+          <t>11/16</t>
         </is>
       </c>
     </row>
@@ -8368,7 +8368,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8422,7 +8422,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>6/16</t>
+          <t>7/16</t>
         </is>
       </c>
     </row>
@@ -8487,7 +8487,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8526,17 +8526,17 @@
       </c>
       <c r="Z68" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
@@ -8606,7 +8606,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8645,22 +8645,22 @@
       </c>
       <c r="Z69" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>7/16</t>
+          <t>5/16</t>
         </is>
       </c>
     </row>
@@ -8725,7 +8725,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8764,22 +8764,22 @@
       </c>
       <c r="Z70" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA70" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>83.2</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>11/16</t>
+          <t>12/16</t>
         </is>
       </c>
     </row>
@@ -8844,7 +8844,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8898,7 +8898,7 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>3/16</t>
+          <t>4/16</t>
         </is>
       </c>
     </row>
@@ -8963,7 +8963,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9002,7 +9002,7 @@
       </c>
       <c r="Z72" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA72" s="2" t="inlineStr">
@@ -9045,32 +9045,36 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr"/>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M73" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -9078,7 +9082,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9102,17 +9106,17 @@
       </c>
       <c r="W73" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y73" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z73" s="2" t="inlineStr">
@@ -9122,12 +9126,12 @@
       </c>
       <c r="AA73" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
@@ -9182,12 +9186,12 @@
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -9197,7 +9201,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9279,32 +9283,36 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:45</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr"/>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M75" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -9312,7 +9320,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9336,17 +9344,17 @@
       </c>
       <c r="W75" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y75" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z75" s="2" t="inlineStr">
@@ -9356,17 +9364,17 @@
       </c>
       <c r="AA75" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>84.3</t>
+          <t>83.2</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>14/16</t>
+          <t>13/16</t>
         </is>
       </c>
     </row>
@@ -9394,32 +9402,36 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:58</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M76" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
           <t>08:20</t>
@@ -9427,7 +9439,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9451,32 +9463,32 @@
       </c>
       <c r="W76" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y76" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z76" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA76" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>80.4</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
@@ -9509,32 +9521,36 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:59</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr"/>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M77" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
           <t>08:40</t>
@@ -9542,7 +9558,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9566,17 +9582,17 @@
       </c>
       <c r="W77" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y77" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z77" s="2" t="inlineStr">
@@ -9586,12 +9602,12 @@
       </c>
       <c r="AA77" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
@@ -9624,32 +9640,36 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M78" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
           <t>07:10</t>
@@ -9657,7 +9677,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9681,37 +9701,37 @@
       </c>
       <c r="W78" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y78" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z78" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA78" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>10/16</t>
+          <t>9/16</t>
         </is>
       </c>
     </row>
@@ -9739,32 +9759,36 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr"/>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M79" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
           <t>12:00</t>
@@ -9772,7 +9796,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9796,17 +9820,17 @@
       </c>
       <c r="W79" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y79" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z79" s="2" t="inlineStr">
@@ -9816,17 +9840,17 @@
       </c>
       <c r="AA79" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>12/16</t>
+          <t>11/16</t>
         </is>
       </c>
     </row>
@@ -9854,32 +9878,36 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:16</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr"/>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M80" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -9887,7 +9915,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9911,17 +9939,17 @@
       </c>
       <c r="W80" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y80" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z80" s="2" t="inlineStr">
@@ -9931,12 +9959,12 @@
       </c>
       <c r="AA80" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
@@ -9969,32 +9997,36 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:16</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr"/>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M81" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -10002,7 +10034,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10026,32 +10058,32 @@
       </c>
       <c r="W81" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y81" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z81" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA81" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
@@ -10117,7 +10149,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10171,7 +10203,7 @@
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>6/16</t>
+          <t>7/16</t>
         </is>
       </c>
     </row>
@@ -10199,32 +10231,36 @@
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:23</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr"/>
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M83" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -10232,7 +10268,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10256,37 +10292,37 @@
       </c>
       <c r="W83" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y83" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z83" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA83" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>7/16</t>
+          <t>5/16</t>
         </is>
       </c>
     </row>
@@ -10314,32 +10350,36 @@
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr"/>
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M84" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
           <t>07:50</t>
@@ -10347,7 +10387,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10371,37 +10411,37 @@
       </c>
       <c r="W84" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y84" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z84" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA84" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA84" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB84" s="2" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>83.2</t>
         </is>
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>11/16</t>
+          <t>12/16</t>
         </is>
       </c>
     </row>
@@ -10462,7 +10502,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10516,7 +10556,7 @@
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>3/16</t>
+          <t>4/16</t>
         </is>
       </c>
     </row>
@@ -10577,7 +10617,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10616,7 +10656,7 @@
       </c>
       <c r="Z86" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA86" s="2" t="inlineStr">
@@ -10692,7 +10732,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10736,12 +10776,12 @@
       </c>
       <c r="AA87" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="AC87" s="2" t="inlineStr">
@@ -10807,7 +10847,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10922,7 +10962,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -10966,17 +11006,707 @@
       </c>
       <c r="AA89" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB89" s="2" t="inlineStr">
         <is>
-          <t>84.3</t>
+          <t>83.2</t>
         </is>
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>14/16</t>
+          <t>13/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr"/>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>19:22</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr"/>
+      <c r="K90" s="2" t="inlineStr"/>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr"/>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P90" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q90" s="2" t="inlineStr"/>
+      <c r="R90" s="2" t="inlineStr"/>
+      <c r="S90" s="2" t="inlineStr"/>
+      <c r="T90" s="2" t="inlineStr"/>
+      <c r="U90" s="2" t="inlineStr">
+        <is>
+          <t>19:22</t>
+        </is>
+      </c>
+      <c r="V90" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W90" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y90" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z90" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA90" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB90" s="2" t="inlineStr">
+        <is>
+          <t>81.7</t>
+        </is>
+      </c>
+      <c r="AC90" s="2" t="inlineStr">
+        <is>
+          <t>9/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr"/>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>19:35</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr"/>
+      <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr"/>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P91" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q91" s="2" t="inlineStr"/>
+      <c r="R91" s="2" t="inlineStr"/>
+      <c r="S91" s="2" t="inlineStr"/>
+      <c r="T91" s="2" t="inlineStr"/>
+      <c r="U91" s="2" t="inlineStr">
+        <is>
+          <t>19:35</t>
+        </is>
+      </c>
+      <c r="V91" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W91" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y91" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z91" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA91" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB91" s="2" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
+      <c r="AC91" s="2" t="inlineStr">
+        <is>
+          <t>3/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr"/>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr"/>
+      <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr"/>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P92" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q92" s="2" t="inlineStr"/>
+      <c r="R92" s="2" t="inlineStr"/>
+      <c r="S92" s="2" t="inlineStr"/>
+      <c r="T92" s="2" t="inlineStr"/>
+      <c r="U92" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="V92" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W92" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y92" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z92" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA92" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB92" s="2" t="inlineStr">
+        <is>
+          <t>81.7</t>
+        </is>
+      </c>
+      <c r="AC92" s="2" t="inlineStr">
+        <is>
+          <t>9/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr"/>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr"/>
+      <c r="K93" s="2" t="inlineStr"/>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr"/>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P93" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q93" s="2" t="inlineStr"/>
+      <c r="R93" s="2" t="inlineStr"/>
+      <c r="S93" s="2" t="inlineStr"/>
+      <c r="T93" s="2" t="inlineStr"/>
+      <c r="U93" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="V93" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W93" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y93" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z93" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA93" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB93" s="2" t="inlineStr">
+        <is>
+          <t>78.2</t>
+        </is>
+      </c>
+      <c r="AC93" s="2" t="inlineStr">
+        <is>
+          <t>5/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr"/>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>20:10</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr"/>
+      <c r="K94" s="2" t="inlineStr"/>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr"/>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>07:50</t>
+        </is>
+      </c>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P94" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q94" s="2" t="inlineStr"/>
+      <c r="R94" s="2" t="inlineStr"/>
+      <c r="S94" s="2" t="inlineStr"/>
+      <c r="T94" s="2" t="inlineStr"/>
+      <c r="U94" s="2" t="inlineStr">
+        <is>
+          <t>20:10</t>
+        </is>
+      </c>
+      <c r="V94" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W94" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y94" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z94" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA94" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB94" s="2" t="inlineStr">
+        <is>
+          <t>83.2</t>
+        </is>
+      </c>
+      <c r="AC94" s="2" t="inlineStr">
+        <is>
+          <t>12/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr"/>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>20:40</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr"/>
+      <c r="K95" s="2" t="inlineStr"/>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr"/>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P95" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q95" s="2" t="inlineStr"/>
+      <c r="R95" s="2" t="inlineStr"/>
+      <c r="S95" s="2" t="inlineStr"/>
+      <c r="T95" s="2" t="inlineStr"/>
+      <c r="U95" s="2" t="inlineStr">
+        <is>
+          <t>20:40</t>
+        </is>
+      </c>
+      <c r="V95" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W95" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y95" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z95" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA95" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB95" s="2" t="inlineStr">
+        <is>
+          <t>78.2</t>
+        </is>
+      </c>
+      <c r="AC95" s="2" t="inlineStr">
+        <is>
+          <t>5/16</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-02-浦东78路.xlsx
+++ b/data/export/2026-10-02-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC95"/>
+  <dimension ref="A1:AC99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>5/16</t>
+          <t>4/16</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>7/16</t>
+          <t>6/16</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1070,12 +1070,12 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>85.7</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1185,17 +1185,17 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>4/16</t>
+          <t>5/16</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>5/16</t>
+          <t>4/16</t>
         </is>
       </c>
     </row>
@@ -1617,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1661,17 +1661,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>83.2</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>13/16</t>
+          <t>11/16</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1790,7 +1790,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>9/16</t>
+          <t>10/16</t>
         </is>
       </c>
     </row>
@@ -1909,7 +1909,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>7/16</t>
+          <t>6/16</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2093,7 +2093,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2142,7 +2142,7 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>83.2</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
@@ -2208,7 +2208,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>85.7</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
@@ -2327,7 +2327,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2371,17 +2371,17 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>4/16</t>
+          <t>5/16</t>
         </is>
       </c>
     </row>
@@ -2557,7 +2557,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
@@ -2676,7 +2676,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2720,17 +2720,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>5/16</t>
+          <t>6/16</t>
         </is>
       </c>
     </row>
@@ -2795,7 +2795,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2834,7 +2834,7 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2958,12 +2958,12 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
@@ -3148,7 +3148,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3192,17 +3192,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>83.2</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>13/16</t>
+          <t>11/16</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3317,7 +3317,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>5/16</t>
+          <t>4/16</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>7/16</t>
+          <t>6/16</t>
         </is>
       </c>
     </row>
@@ -3497,7 +3497,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3551,7 +3551,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>9/16</t>
+          <t>10/16</t>
         </is>
       </c>
     </row>
@@ -3616,7 +3616,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>85.7</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
@@ -3735,7 +3735,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3854,7 +3854,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3898,12 +3898,12 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
@@ -3973,7 +3973,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4022,7 +4022,7 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>83.2</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
@@ -4092,7 +4092,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
@@ -4211,7 +4211,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4255,17 +4255,17 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>5/16</t>
+          <t>6/16</t>
         </is>
       </c>
     </row>
@@ -4330,7 +4330,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4384,7 +4384,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>5/16</t>
+          <t>4/16</t>
         </is>
       </c>
     </row>
@@ -4449,7 +4449,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4488,7 +4488,7 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
@@ -4568,7 +4568,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4622,7 +4622,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>9/16</t>
+          <t>10/16</t>
         </is>
       </c>
     </row>
@@ -4802,7 +4802,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4921,7 +4921,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4970,7 +4970,7 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>83.2</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
@@ -5094,7 +5094,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>7/16</t>
+          <t>6/16</t>
         </is>
       </c>
     </row>
@@ -5159,7 +5159,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5203,17 +5203,17 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>5/16</t>
+          <t>6/16</t>
         </is>
       </c>
     </row>
@@ -5278,7 +5278,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5322,12 +5322,12 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
@@ -5397,7 +5397,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5436,7 +5436,7 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
@@ -5516,7 +5516,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5560,12 +5560,12 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
@@ -5754,7 +5754,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5793,14 +5793,14 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA45" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
           <t>83.0</t>
@@ -5808,7 +5808,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>11/16</t>
+          <t>12/16</t>
         </is>
       </c>
     </row>
@@ -5927,7 +5927,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>7/16</t>
+          <t>6/16</t>
         </is>
       </c>
     </row>
@@ -5992,7 +5992,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6036,17 +6036,17 @@
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>4/16</t>
+          <t>5/16</t>
         </is>
       </c>
     </row>
@@ -6111,7 +6111,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6155,12 +6155,12 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
@@ -6230,7 +6230,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6274,12 +6274,12 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>85.7</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
@@ -6349,7 +6349,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6393,12 +6393,12 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
@@ -6468,7 +6468,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6512,17 +6512,17 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>83.2</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>13/16</t>
+          <t>11/16</t>
         </is>
       </c>
     </row>
@@ -6587,7 +6587,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6626,14 +6626,14 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA52" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
           <t>83.0</t>
@@ -6641,7 +6641,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>11/16</t>
+          <t>12/16</t>
         </is>
       </c>
     </row>
@@ -6706,7 +6706,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6760,7 +6760,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>9/16</t>
+          <t>10/16</t>
         </is>
       </c>
     </row>
@@ -6944,7 +6944,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6988,17 +6988,17 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>4/16</t>
+          <t>5/16</t>
         </is>
       </c>
     </row>
@@ -7117,7 +7117,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>7/16</t>
+          <t>6/16</t>
         </is>
       </c>
     </row>
@@ -7182,7 +7182,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7231,7 +7231,7 @@
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>83.2</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
@@ -7301,7 +7301,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>85.7</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
@@ -7420,7 +7420,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7464,17 +7464,17 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>5/16</t>
+          <t>6/16</t>
         </is>
       </c>
     </row>
@@ -7539,7 +7539,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7583,17 +7583,17 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>83.2</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>13/16</t>
+          <t>11/16</t>
         </is>
       </c>
     </row>
@@ -7654,7 +7654,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7698,12 +7698,12 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
@@ -7773,7 +7773,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7827,7 +7827,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>9/16</t>
+          <t>10/16</t>
         </is>
       </c>
     </row>
@@ -7892,7 +7892,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7936,12 +7936,12 @@
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
@@ -8011,7 +8011,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8050,7 +8050,7 @@
       </c>
       <c r="Z64" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA64" s="2" t="inlineStr">
@@ -8249,7 +8249,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8288,14 +8288,14 @@
       </c>
       <c r="Z66" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA66" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
           <t>83.0</t>
@@ -8303,7 +8303,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>11/16</t>
+          <t>12/16</t>
         </is>
       </c>
     </row>
@@ -8422,7 +8422,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>7/16</t>
+          <t>6/16</t>
         </is>
       </c>
     </row>
@@ -8487,7 +8487,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8606,7 +8606,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8660,7 +8660,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>5/16</t>
+          <t>4/16</t>
         </is>
       </c>
     </row>
@@ -8725,7 +8725,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8774,7 +8774,7 @@
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>83.2</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
@@ -8844,7 +8844,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8888,17 +8888,17 @@
       </c>
       <c r="AA71" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>4/16</t>
+          <t>5/16</t>
         </is>
       </c>
     </row>
@@ -8963,7 +8963,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9007,17 +9007,17 @@
       </c>
       <c r="AA72" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>5/16</t>
+          <t>6/16</t>
         </is>
       </c>
     </row>
@@ -9082,7 +9082,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9126,12 +9126,12 @@
       </c>
       <c r="AA73" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>85.7</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
@@ -9201,7 +9201,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9245,12 +9245,12 @@
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
@@ -9320,7 +9320,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9364,17 +9364,17 @@
       </c>
       <c r="AA75" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>83.2</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>13/16</t>
+          <t>11/16</t>
         </is>
       </c>
     </row>
@@ -9439,7 +9439,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="AA76" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
@@ -9558,7 +9558,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9597,7 +9597,7 @@
       </c>
       <c r="Z77" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA77" s="2" t="inlineStr">
@@ -9677,7 +9677,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9731,7 +9731,7 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>9/16</t>
+          <t>10/16</t>
         </is>
       </c>
     </row>
@@ -9796,7 +9796,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9835,14 +9835,14 @@
       </c>
       <c r="Z79" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA79" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
           <t>83.0</t>
@@ -9850,7 +9850,7 @@
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>11/16</t>
+          <t>12/16</t>
         </is>
       </c>
     </row>
@@ -10034,7 +10034,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10203,7 +10203,7 @@
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>7/16</t>
+          <t>6/16</t>
         </is>
       </c>
     </row>
@@ -10268,7 +10268,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10322,7 +10322,7 @@
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>5/16</t>
+          <t>4/16</t>
         </is>
       </c>
     </row>
@@ -10360,24 +10360,24 @@
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>19:44</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>85分钟</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr"/>
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -10387,7 +10387,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10436,7 +10436,7 @@
       </c>
       <c r="AB84" s="2" t="inlineStr">
         <is>
-          <t>83.2</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC84" s="2" t="inlineStr">
@@ -10469,32 +10469,36 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:49</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr"/>
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M85" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -10502,7 +10506,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10526,17 +10530,17 @@
       </c>
       <c r="W85" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y85" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z85" s="2" t="inlineStr">
@@ -10546,17 +10550,17 @@
       </c>
       <c r="AA85" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>4/16</t>
+          <t>5/16</t>
         </is>
       </c>
     </row>
@@ -10584,32 +10588,36 @@
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr"/>
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M86" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
           <t>08:20</t>
@@ -10617,7 +10625,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10641,17 +10649,17 @@
       </c>
       <c r="W86" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y86" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z86" s="2" t="inlineStr">
@@ -10661,17 +10669,17 @@
       </c>
       <c r="AA86" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB86" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>5/16</t>
+          <t>6/16</t>
         </is>
       </c>
     </row>
@@ -10699,32 +10707,36 @@
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:12</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr"/>
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M87" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -10732,7 +10744,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10756,17 +10768,17 @@
       </c>
       <c r="W87" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y87" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z87" s="2" t="inlineStr">
@@ -10776,12 +10788,12 @@
       </c>
       <c r="AA87" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>85.7</t>
         </is>
       </c>
       <c r="AC87" s="2" t="inlineStr">
@@ -10814,32 +10826,36 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr"/>
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M88" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N88" s="2" t="inlineStr">
         <is>
           <t>08:20</t>
@@ -10847,7 +10863,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10871,17 +10887,17 @@
       </c>
       <c r="W88" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y88" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z88" s="2" t="inlineStr">
@@ -10891,12 +10907,12 @@
       </c>
       <c r="AA88" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB88" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC88" s="2" t="inlineStr">
@@ -10929,32 +10945,36 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr"/>
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M89" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -10962,7 +10982,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -10986,17 +11006,17 @@
       </c>
       <c r="W89" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y89" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z89" s="2" t="inlineStr">
@@ -11006,17 +11026,17 @@
       </c>
       <c r="AA89" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB89" s="2" t="inlineStr">
         <is>
-          <t>83.2</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>13/16</t>
+          <t>11/16</t>
         </is>
       </c>
     </row>
@@ -11044,32 +11064,36 @@
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr"/>
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M90" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
           <t>08:20</t>
@@ -11077,7 +11101,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11101,17 +11125,17 @@
       </c>
       <c r="W90" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y90" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z90" s="2" t="inlineStr">
@@ -11121,12 +11145,12 @@
       </c>
       <c r="AA90" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB90" s="2" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC90" s="2" t="inlineStr">
@@ -11192,7 +11216,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11307,7 +11331,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11361,7 +11385,7 @@
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>9/16</t>
+          <t>10/16</t>
         </is>
       </c>
     </row>
@@ -11422,7 +11446,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11476,7 +11500,7 @@
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>5/16</t>
+          <t>4/16</t>
         </is>
       </c>
     </row>
@@ -11484,22 +11508,22 @@
       <c r="A94" s="2" t="inlineStr"/>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A35616D</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>19:45</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="inlineStr">
-        <is>
-          <t>20:10</t>
-        </is>
-      </c>
-      <c r="E94" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
@@ -11532,12 +11556,12 @@
       <c r="M94" s="2" t="inlineStr"/>
       <c r="N94" s="2" t="inlineStr">
         <is>
-          <t>07:50</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11551,7 +11575,7 @@
       <c r="T94" s="2" t="inlineStr"/>
       <c r="U94" s="2" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="V94" s="2" t="inlineStr">
@@ -11581,17 +11605,17 @@
       </c>
       <c r="AA94" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB94" s="2" t="inlineStr">
         <is>
-          <t>83.2</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>12/16</t>
+          <t>8/16</t>
         </is>
       </c>
     </row>
@@ -11599,22 +11623,22 @@
       <c r="A95" s="2" t="inlineStr"/>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>沪A56123D</t>
+          <t>沪A35172D</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>19:58</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="D95" s="2" t="inlineStr">
-        <is>
-          <t>20:40</t>
-        </is>
-      </c>
-      <c r="E95" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr">
@@ -11647,12 +11671,12 @@
       <c r="M95" s="2" t="inlineStr"/>
       <c r="N95" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11666,47 +11690,507 @@
       <c r="T95" s="2" t="inlineStr"/>
       <c r="U95" s="2" t="inlineStr">
         <is>
+          <t>19:58</t>
+        </is>
+      </c>
+      <c r="V95" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W95" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y95" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z95" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA95" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB95" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
+      <c r="AC95" s="2" t="inlineStr">
+        <is>
+          <t>12/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr"/>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>20:10</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr"/>
+      <c r="K96" s="2" t="inlineStr"/>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr"/>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>07:50</t>
+        </is>
+      </c>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>20:20</t>
+        </is>
+      </c>
+      <c r="P96" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q96" s="2" t="inlineStr"/>
+      <c r="R96" s="2" t="inlineStr"/>
+      <c r="S96" s="2" t="inlineStr"/>
+      <c r="T96" s="2" t="inlineStr"/>
+      <c r="U96" s="2" t="inlineStr">
+        <is>
+          <t>20:10</t>
+        </is>
+      </c>
+      <c r="V96" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W96" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y96" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z96" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA96" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB96" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
+      <c r="AC96" s="2" t="inlineStr">
+        <is>
+          <t>12/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr"/>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
           <t>20:40</t>
         </is>
       </c>
-      <c r="V95" s="2" t="inlineStr">
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr"/>
+      <c r="K97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr"/>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>20:20</t>
+        </is>
+      </c>
+      <c r="P97" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q97" s="2" t="inlineStr"/>
+      <c r="R97" s="2" t="inlineStr"/>
+      <c r="S97" s="2" t="inlineStr"/>
+      <c r="T97" s="2" t="inlineStr"/>
+      <c r="U97" s="2" t="inlineStr">
+        <is>
+          <t>20:40</t>
+        </is>
+      </c>
+      <c r="V97" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W95" s="2" t="inlineStr">
+      <c r="W97" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X95" s="2" t="inlineStr">
+      <c r="X97" s="2" t="inlineStr">
         <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Y95" s="2" t="inlineStr">
+      <c r="Y97" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z95" s="2" t="inlineStr">
+      <c r="Z97" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA95" s="2" t="inlineStr">
+      <c r="AA97" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB97" s="2" t="inlineStr">
+        <is>
+          <t>78.8</t>
+        </is>
+      </c>
+      <c r="AC97" s="2" t="inlineStr">
+        <is>
+          <t>6/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr"/>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>21:10</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr"/>
+      <c r="K98" s="2" t="inlineStr"/>
+      <c r="L98" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr"/>
+      <c r="N98" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>20:20</t>
+        </is>
+      </c>
+      <c r="P98" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q98" s="2" t="inlineStr"/>
+      <c r="R98" s="2" t="inlineStr"/>
+      <c r="S98" s="2" t="inlineStr"/>
+      <c r="T98" s="2" t="inlineStr"/>
+      <c r="U98" s="2" t="inlineStr">
+        <is>
+          <t>21:10</t>
+        </is>
+      </c>
+      <c r="V98" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W98" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y98" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z98" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA98" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AB95" s="2" t="inlineStr">
-        <is>
-          <t>78.2</t>
-        </is>
-      </c>
-      <c r="AC95" s="2" t="inlineStr">
-        <is>
-          <t>5/16</t>
+      <c r="AB98" s="2" t="inlineStr">
+        <is>
+          <t>79.6</t>
+        </is>
+      </c>
+      <c r="AC98" s="2" t="inlineStr">
+        <is>
+          <t>8/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr"/>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>21:40</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr"/>
+      <c r="K99" s="2" t="inlineStr"/>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr"/>
+      <c r="N99" s="2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>20:20</t>
+        </is>
+      </c>
+      <c r="P99" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q99" s="2" t="inlineStr"/>
+      <c r="R99" s="2" t="inlineStr"/>
+      <c r="S99" s="2" t="inlineStr"/>
+      <c r="T99" s="2" t="inlineStr"/>
+      <c r="U99" s="2" t="inlineStr">
+        <is>
+          <t>21:40</t>
+        </is>
+      </c>
+      <c r="V99" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W99" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y99" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z99" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA99" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB99" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
+      <c r="AC99" s="2" t="inlineStr">
+        <is>
+          <t>12/16</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-02-浦东78路.xlsx
+++ b/data/export/2026-10-02-浦东78路.xlsx
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>6/16</t>
+          <t>7/16</t>
         </is>
       </c>
     </row>
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>5/16</t>
+          <t>6/16</t>
         </is>
       </c>
     </row>
@@ -1617,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1666,12 +1666,12 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>82.6</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>11/16</t>
+          <t>12/16</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1780,12 +1780,12 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>81.6</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
@@ -1909,7 +1909,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>6/16</t>
+          <t>7/16</t>
         </is>
       </c>
     </row>
@@ -2093,7 +2093,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2137,17 +2137,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>81.9</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>12/16</t>
+          <t>11/16</t>
         </is>
       </c>
     </row>
@@ -2381,7 +2381,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>5/16</t>
+          <t>6/16</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2720,17 +2720,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>6/16</t>
+          <t>5/16</t>
         </is>
       </c>
     </row>
@@ -2795,7 +2795,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2839,12 +2839,12 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2963,7 +2963,7 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
@@ -3148,7 +3148,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3197,12 +3197,12 @@
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>82.6</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>11/16</t>
+          <t>12/16</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>6/16</t>
+          <t>7/16</t>
         </is>
       </c>
     </row>
@@ -3497,7 +3497,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3541,12 +3541,12 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>81.6</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
@@ -3973,7 +3973,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4017,17 +4017,17 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>81.9</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>12/16</t>
+          <t>11/16</t>
         </is>
       </c>
     </row>
@@ -4092,7 +4092,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4141,7 +4141,7 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
@@ -4211,7 +4211,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4255,17 +4255,17 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>6/16</t>
+          <t>5/16</t>
         </is>
       </c>
     </row>
@@ -4449,7 +4449,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4493,12 +4493,12 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
@@ -4568,7 +4568,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4612,12 +4612,12 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>81.6</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
@@ -4921,7 +4921,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4965,17 +4965,17 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>81.9</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>12/16</t>
+          <t>11/16</t>
         </is>
       </c>
     </row>
@@ -5094,7 +5094,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>6/16</t>
+          <t>7/16</t>
         </is>
       </c>
     </row>
@@ -5159,7 +5159,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5203,17 +5203,17 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>6/16</t>
+          <t>5/16</t>
         </is>
       </c>
     </row>
@@ -5397,7 +5397,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
@@ -5516,7 +5516,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5565,7 +5565,7 @@
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
@@ -5754,7 +5754,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5798,7 +5798,7 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
@@ -5808,7 +5808,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>12/16</t>
+          <t>13/16</t>
         </is>
       </c>
     </row>
@@ -5927,7 +5927,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>6/16</t>
+          <t>7/16</t>
         </is>
       </c>
     </row>
@@ -6046,7 +6046,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>5/16</t>
+          <t>6/16</t>
         </is>
       </c>
     </row>
@@ -6349,7 +6349,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6398,7 +6398,7 @@
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
@@ -6468,7 +6468,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6517,12 +6517,12 @@
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>82.6</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>11/16</t>
+          <t>12/16</t>
         </is>
       </c>
     </row>
@@ -6587,7 +6587,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6631,7 +6631,7 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
@@ -6641,7 +6641,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>12/16</t>
+          <t>13/16</t>
         </is>
       </c>
     </row>
@@ -6706,7 +6706,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6750,12 +6750,12 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>81.6</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
@@ -6998,7 +6998,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>5/16</t>
+          <t>6/16</t>
         </is>
       </c>
     </row>
@@ -7117,7 +7117,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>6/16</t>
+          <t>7/16</t>
         </is>
       </c>
     </row>
@@ -7182,7 +7182,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7226,17 +7226,17 @@
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>81.9</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>12/16</t>
+          <t>11/16</t>
         </is>
       </c>
     </row>
@@ -7420,7 +7420,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7464,17 +7464,17 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>6/16</t>
+          <t>5/16</t>
         </is>
       </c>
     </row>
@@ -7539,7 +7539,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7588,12 +7588,12 @@
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>82.6</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>11/16</t>
+          <t>12/16</t>
         </is>
       </c>
     </row>
@@ -7773,7 +7773,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7817,12 +7817,12 @@
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>81.6</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
@@ -7892,7 +7892,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7941,7 +7941,7 @@
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
@@ -8011,7 +8011,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8055,12 +8055,12 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
@@ -8249,7 +8249,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8293,7 +8293,7 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
@@ -8303,7 +8303,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>12/16</t>
+          <t>13/16</t>
         </is>
       </c>
     </row>
@@ -8422,7 +8422,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>6/16</t>
+          <t>7/16</t>
         </is>
       </c>
     </row>
@@ -8725,7 +8725,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8769,17 +8769,17 @@
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>81.9</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>12/16</t>
+          <t>11/16</t>
         </is>
       </c>
     </row>
@@ -8898,7 +8898,7 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>5/16</t>
+          <t>6/16</t>
         </is>
       </c>
     </row>
@@ -8963,7 +8963,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9007,17 +9007,17 @@
       </c>
       <c r="AA72" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>6/16</t>
+          <t>5/16</t>
         </is>
       </c>
     </row>
@@ -9320,7 +9320,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9369,12 +9369,12 @@
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>82.6</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>11/16</t>
+          <t>12/16</t>
         </is>
       </c>
     </row>
@@ -9439,7 +9439,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9488,7 +9488,7 @@
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
@@ -9558,7 +9558,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9602,12 +9602,12 @@
       </c>
       <c r="AA77" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
@@ -9677,7 +9677,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9721,12 +9721,12 @@
       </c>
       <c r="AA78" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>81.6</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
@@ -9796,7 +9796,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9840,7 +9840,7 @@
       </c>
       <c r="AA79" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB79" s="2" t="inlineStr">
@@ -9850,7 +9850,7 @@
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>12/16</t>
+          <t>13/16</t>
         </is>
       </c>
     </row>
@@ -10203,7 +10203,7 @@
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>6/16</t>
+          <t>7/16</t>
         </is>
       </c>
     </row>
@@ -10387,7 +10387,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10431,17 +10431,17 @@
       </c>
       <c r="AA84" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB84" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>81.9</t>
         </is>
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>12/16</t>
+          <t>11/16</t>
         </is>
       </c>
     </row>
@@ -10560,7 +10560,7 @@
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>5/16</t>
+          <t>6/16</t>
         </is>
       </c>
     </row>
@@ -10625,7 +10625,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10669,17 +10669,17 @@
       </c>
       <c r="AA86" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB86" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>6/16</t>
+          <t>5/16</t>
         </is>
       </c>
     </row>
@@ -10955,24 +10955,24 @@
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>20:31</t>
+          <t>20:35</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>76分钟</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr"/>
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
@@ -10982,7 +10982,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11031,12 +11031,12 @@
       </c>
       <c r="AB89" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>82.6</t>
         </is>
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>11/16</t>
+          <t>12/16</t>
         </is>
       </c>
     </row>
@@ -11074,12 +11074,12 @@
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>79分钟</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr"/>
@@ -11101,7 +11101,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11150,7 +11150,7 @@
       </c>
       <c r="AB90" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="AC90" s="2" t="inlineStr">
@@ -11298,32 +11298,36 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr"/>
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M92" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
           <t>07:10</t>
@@ -11331,7 +11335,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11355,17 +11359,17 @@
       </c>
       <c r="W92" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y92" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z92" s="2" t="inlineStr">
@@ -11375,12 +11379,12 @@
       </c>
       <c r="AA92" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB92" s="2" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>81.6</t>
         </is>
       </c>
       <c r="AC92" s="2" t="inlineStr">
@@ -11528,32 +11532,36 @@
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:04</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr"/>
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M94" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N94" s="2" t="inlineStr">
         <is>
           <t>08:40</t>
@@ -11561,7 +11569,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11585,17 +11593,17 @@
       </c>
       <c r="W94" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y94" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z94" s="2" t="inlineStr">
@@ -11605,12 +11613,12 @@
       </c>
       <c r="AA94" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB94" s="2" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC94" s="2" t="inlineStr">
@@ -11643,32 +11651,36 @@
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr"/>
       <c r="K95" s="2" t="inlineStr"/>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M95" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N95" s="2" t="inlineStr">
         <is>
           <t>12:00</t>
@@ -11676,7 +11688,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11700,17 +11712,17 @@
       </c>
       <c r="W95" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y95" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z95" s="2" t="inlineStr">
@@ -11720,7 +11732,7 @@
       </c>
       <c r="AA95" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB95" s="2" t="inlineStr">
@@ -11730,7 +11742,7 @@
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>12/16</t>
+          <t>13/16</t>
         </is>
       </c>
     </row>
@@ -11758,32 +11770,36 @@
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:25</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr"/>
       <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M96" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N96" s="2" t="inlineStr">
         <is>
           <t>07:50</t>
@@ -11791,7 +11807,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11815,17 +11831,17 @@
       </c>
       <c r="W96" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y96" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z96" s="2" t="inlineStr">
@@ -11835,17 +11851,17 @@
       </c>
       <c r="AA96" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB96" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>81.9</t>
         </is>
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>12/16</t>
+          <t>11/16</t>
         </is>
       </c>
     </row>
@@ -11873,32 +11889,36 @@
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:56</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr"/>
       <c r="K97" s="2" t="inlineStr"/>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M97" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N97" s="2" t="inlineStr">
         <is>
           <t>08:20</t>
@@ -11906,7 +11926,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11930,17 +11950,17 @@
       </c>
       <c r="W97" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y97" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z97" s="2" t="inlineStr">
@@ -11950,17 +11970,17 @@
       </c>
       <c r="AA97" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB97" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>6/16</t>
+          <t>5/16</t>
         </is>
       </c>
     </row>
@@ -12021,7 +12041,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12065,12 +12085,12 @@
       </c>
       <c r="AA98" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB98" s="2" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC98" s="2" t="inlineStr">
@@ -12136,7 +12156,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12180,7 +12200,7 @@
       </c>
       <c r="AA99" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB99" s="2" t="inlineStr">
@@ -12190,7 +12210,7 @@
       </c>
       <c r="AC99" s="2" t="inlineStr">
         <is>
-          <t>12/16</t>
+          <t>13/16</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-02-浦东78路.xlsx
+++ b/data/export/2026-10-02-浦东78路.xlsx
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>7/16</t>
+          <t>8/16</t>
         </is>
       </c>
     </row>
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>6/16</t>
+          <t>7/16</t>
         </is>
       </c>
     </row>
@@ -1909,7 +1909,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>7/16</t>
+          <t>8/16</t>
         </is>
       </c>
     </row>
@@ -2381,7 +2381,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>6/16</t>
+          <t>7/16</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2725,12 +2725,12 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>78.4</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>5/16</t>
+          <t>6/16</t>
         </is>
       </c>
     </row>
@@ -2795,7 +2795,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2839,17 +2839,17 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>8/16</t>
+          <t>5/16</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>7/16</t>
+          <t>8/16</t>
         </is>
       </c>
     </row>
@@ -4211,7 +4211,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4260,12 +4260,12 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>78.4</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>5/16</t>
+          <t>6/16</t>
         </is>
       </c>
     </row>
@@ -4449,7 +4449,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4493,17 +4493,17 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>8/16</t>
+          <t>5/16</t>
         </is>
       </c>
     </row>
@@ -5094,7 +5094,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>7/16</t>
+          <t>8/16</t>
         </is>
       </c>
     </row>
@@ -5159,7 +5159,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5208,12 +5208,12 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>78.4</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>5/16</t>
+          <t>6/16</t>
         </is>
       </c>
     </row>
@@ -5397,7 +5397,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5441,17 +5441,17 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>8/16</t>
+          <t>5/16</t>
         </is>
       </c>
     </row>
@@ -5754,7 +5754,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5927,7 +5927,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>7/16</t>
+          <t>8/16</t>
         </is>
       </c>
     </row>
@@ -6046,7 +6046,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>6/16</t>
+          <t>7/16</t>
         </is>
       </c>
     </row>
@@ -6587,7 +6587,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6998,7 +6998,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>6/16</t>
+          <t>7/16</t>
         </is>
       </c>
     </row>
@@ -7117,7 +7117,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>7/16</t>
+          <t>8/16</t>
         </is>
       </c>
     </row>
@@ -7420,7 +7420,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7469,12 +7469,12 @@
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>78.4</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>5/16</t>
+          <t>6/16</t>
         </is>
       </c>
     </row>
@@ -8011,7 +8011,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8055,17 +8055,17 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>8/16</t>
+          <t>5/16</t>
         </is>
       </c>
     </row>
@@ -8249,7 +8249,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8422,7 +8422,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>7/16</t>
+          <t>8/16</t>
         </is>
       </c>
     </row>
@@ -8898,7 +8898,7 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>6/16</t>
+          <t>7/16</t>
         </is>
       </c>
     </row>
@@ -8963,7 +8963,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9012,12 +9012,12 @@
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>78.4</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>5/16</t>
+          <t>6/16</t>
         </is>
       </c>
     </row>
@@ -9558,7 +9558,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9602,17 +9602,17 @@
       </c>
       <c r="AA77" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>8/16</t>
+          <t>5/16</t>
         </is>
       </c>
     </row>
@@ -9796,7 +9796,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -10203,7 +10203,7 @@
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>7/16</t>
+          <t>8/16</t>
         </is>
       </c>
     </row>
@@ -10560,7 +10560,7 @@
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>6/16</t>
+          <t>7/16</t>
         </is>
       </c>
     </row>
@@ -10625,7 +10625,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10674,12 +10674,12 @@
       </c>
       <c r="AB86" s="2" t="inlineStr">
         <is>
-          <t>78.4</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>5/16</t>
+          <t>6/16</t>
         </is>
       </c>
     </row>
@@ -11569,7 +11569,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11613,17 +11613,17 @@
       </c>
       <c r="AA94" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB94" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>8/16</t>
+          <t>5/16</t>
         </is>
       </c>
     </row>
@@ -11688,7 +11688,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11899,12 +11899,12 @@
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>21:56</t>
+          <t>21:57</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>76分钟</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr"/>
@@ -11926,7 +11926,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11975,12 +11975,12 @@
       </c>
       <c r="AB97" s="2" t="inlineStr">
         <is>
-          <t>78.4</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>5/16</t>
+          <t>6/16</t>
         </is>
       </c>
     </row>
@@ -12008,32 +12008,36 @@
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22:22</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr"/>
       <c r="K98" s="2" t="inlineStr"/>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M98" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N98" s="2" t="inlineStr">
         <is>
           <t>08:40</t>
@@ -12041,7 +12045,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12065,17 +12069,17 @@
       </c>
       <c r="W98" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y98" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z98" s="2" t="inlineStr">
@@ -12085,17 +12089,17 @@
       </c>
       <c r="AA98" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB98" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="AC98" s="2" t="inlineStr">
         <is>
-          <t>8/16</t>
+          <t>5/16</t>
         </is>
       </c>
     </row>
@@ -12156,7 +12160,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
